--- a/grupos/2ARHM - Estadisticos 20212.xlsx
+++ b/grupos/2ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="161">
   <si>
     <t>Materia</t>
   </si>
@@ -200,10 +200,10 @@
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
+    <t>Morales Vallejo Jorge Luis</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
     <t>Mendoza Velazquez Laura Elena</t>
@@ -992,7 +992,7 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>-1</v>
@@ -1046,7 +1046,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>-1</v>
@@ -1069,7 +1069,7 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>-1</v>
@@ -1123,7 +1123,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>-1</v>
@@ -1146,7 +1146,7 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E6">
         <v>-1</v>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>-1</v>
@@ -1223,7 +1223,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>-1</v>
@@ -1277,7 +1277,7 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>-1</v>
@@ -1300,7 +1300,7 @@
         <v>8</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>-1</v>
@@ -1354,7 +1354,7 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>-1</v>
@@ -1377,7 +1377,7 @@
         <v>6</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <v>-1</v>
@@ -1431,7 +1431,7 @@
         <v>6</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>-1</v>
@@ -1454,7 +1454,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>-1</v>
@@ -1508,7 +1508,7 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>-1</v>
@@ -1531,7 +1531,7 @@
         <v>8</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <v>-1</v>
@@ -1585,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>-1</v>
@@ -1608,7 +1608,7 @@
         <v>9</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E12">
         <v>-1</v>
@@ -1662,7 +1662,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>-1</v>
@@ -1685,7 +1685,7 @@
         <v>9</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>-1</v>
@@ -1739,7 +1739,7 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>-1</v>
@@ -1762,7 +1762,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>-1</v>
@@ -1816,7 +1816,7 @@
         <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>-1</v>
@@ -1839,7 +1839,7 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>-1</v>
@@ -1893,7 +1893,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>-1</v>
@@ -1916,7 +1916,7 @@
         <v>9</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>-1</v>
@@ -1970,7 +1970,7 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>-1</v>
@@ -1993,7 +1993,7 @@
         <v>8</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E17">
         <v>-1</v>
@@ -2047,7 +2047,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>-1</v>
@@ -2070,7 +2070,7 @@
         <v>8</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E18">
         <v>-1</v>
@@ -2124,7 +2124,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>-1</v>
@@ -2147,7 +2147,7 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>-1</v>
@@ -2201,7 +2201,7 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>-1</v>
@@ -2221,7 +2221,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>-1</v>
@@ -2275,7 +2275,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2301,7 +2301,7 @@
         <v>8</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>-1</v>
@@ -2355,7 +2355,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>-1</v>
@@ -2455,7 +2455,7 @@
         <v>8</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>-1</v>
@@ -2509,7 +2509,7 @@
         <v>8</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>-1</v>
@@ -2532,7 +2532,7 @@
         <v>9</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E24">
         <v>-1</v>
@@ -2586,7 +2586,7 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>-1</v>
@@ -2609,7 +2609,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>-1</v>
@@ -2663,7 +2663,7 @@
         <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>-1</v>
@@ -2683,7 +2683,7 @@
         <v>5</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>-1</v>
@@ -2737,7 +2737,7 @@
         <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -2763,7 +2763,7 @@
         <v>10</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E27">
         <v>-1</v>
@@ -2817,7 +2817,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>-1</v>
@@ -2840,7 +2840,7 @@
         <v>10</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E28">
         <v>-1</v>
@@ -2894,7 +2894,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>-1</v>
@@ -2917,7 +2917,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E29">
         <v>-1</v>
@@ -2971,7 +2971,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>-1</v>
@@ -2994,7 +2994,7 @@
         <v>6</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E30">
         <v>-1</v>
@@ -3048,7 +3048,7 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>-1</v>
@@ -3071,7 +3071,7 @@
         <v>10</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E31">
         <v>-1</v>
@@ -3125,7 +3125,7 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>-1</v>
@@ -3148,7 +3148,7 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E32">
         <v>-1</v>
@@ -3202,7 +3202,7 @@
         <v>9</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>-1</v>
@@ -3225,7 +3225,7 @@
         <v>8</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E33">
         <v>-1</v>
@@ -3279,7 +3279,7 @@
         <v>8</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>-1</v>
@@ -3302,7 +3302,7 @@
         <v>8</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E34">
         <v>-1</v>
@@ -3356,7 +3356,7 @@
         <v>8</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>-1</v>
@@ -3379,7 +3379,7 @@
         <v>9</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E35">
         <v>-1</v>
@@ -3433,7 +3433,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>-1</v>
@@ -3456,7 +3456,7 @@
         <v>10</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E36">
         <v>-1</v>
@@ -3510,7 +3510,7 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W36">
         <v>-1</v>
@@ -3530,7 +3530,7 @@
         <v>5</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>-1</v>
@@ -3584,7 +3584,7 @@
         <v>5</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V37">
         <v>-1</v>
@@ -3610,7 +3610,7 @@
         <v>10</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E38">
         <v>-1</v>
@@ -3664,7 +3664,7 @@
         <v>10</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>-1</v>
@@ -3687,7 +3687,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E39">
         <v>-1</v>
@@ -3741,7 +3741,7 @@
         <v>7</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W39">
         <v>-1</v>
@@ -3764,7 +3764,7 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E40">
         <v>-1</v>
@@ -3818,7 +3818,7 @@
         <v>7</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W40">
         <v>-1</v>
@@ -3941,7 +3941,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -3950,27 +3950,30 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>8.699999999999999</v>
+      </c>
       <c r="I4">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -3991,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>4</v>
@@ -4046,22 +4049,22 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7">
         <v>91.89</v>
       </c>
       <c r="G7">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="H7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="H7">
-        <v>8.4</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
       <c r="J7">
-        <v>8.109999999999999</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4071,7 +4074,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4140,22 +4143,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920215</v>
+        <v>21330051920216</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4172,64 +4175,64 @@
         <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920216</v>
+        <v>21330051920217</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920216</v>
+        <v>21330051920217</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920217</v>
+        <v>21330051920218</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -4240,16 +4243,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920217</v>
+        <v>21330051920218</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4260,96 +4263,96 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920217</v>
+        <v>21330051920219</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920218</v>
+        <v>21330051920219</v>
       </c>
       <c r="B11" t="s">
         <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920218</v>
+        <v>21330051920220</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920218</v>
+        <v>21330051920220</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920219</v>
+        <v>21330051920221</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -4360,16 +4363,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920219</v>
+        <v>21330051920221</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4380,96 +4383,96 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920219</v>
+        <v>21330051920230</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920220</v>
+        <v>21330051920230</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920220</v>
+        <v>21330051920231</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920220</v>
+        <v>21330051920231</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920221</v>
+        <v>21330051920232</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -4480,16 +4483,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920221</v>
+        <v>21330051920232</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4500,96 +4503,96 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920221</v>
+        <v>21330051920233</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920230</v>
+        <v>21330051920233</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920230</v>
+        <v>21330051920042</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920230</v>
+        <v>21330051920042</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920231</v>
+        <v>21330051920044</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -4600,16 +4603,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920231</v>
+        <v>21330051920044</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -4620,96 +4623,96 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920231</v>
+        <v>21330051920234</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920232</v>
+        <v>21330051920234</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920232</v>
+        <v>21330051920235</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920232</v>
+        <v>21330051920235</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E31" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920233</v>
+        <v>21330051920236</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -4720,16 +4723,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920233</v>
+        <v>21330051920236</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -4740,19 +4743,19 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920233</v>
+        <v>21330051920359</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
         <v>60</v>
@@ -4760,16 +4763,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920042</v>
+        <v>21330051920359</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -4780,16 +4783,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920042</v>
+        <v>21330051920359</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -4800,216 +4803,216 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920042</v>
+        <v>21330051920359</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E37" t="s">
         <v>7</v>
       </c>
       <c r="F37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920044</v>
+        <v>21330051920237</v>
       </c>
       <c r="B38" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" t="s">
         <v>78</v>
       </c>
-      <c r="C38" t="s">
-        <v>110</v>
-      </c>
       <c r="D38" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920044</v>
+        <v>21330051920237</v>
       </c>
       <c r="B39" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" t="s">
         <v>78</v>
       </c>
-      <c r="C39" t="s">
-        <v>110</v>
-      </c>
       <c r="D39" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>21330051920044</v>
+        <v>21330051920237</v>
       </c>
       <c r="B40" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" t="s">
         <v>78</v>
       </c>
-      <c r="C40" t="s">
-        <v>110</v>
-      </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920234</v>
+        <v>21330051920237</v>
       </c>
       <c r="B41" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" t="s">
         <v>78</v>
       </c>
-      <c r="C41" t="s">
-        <v>111</v>
-      </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F41" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920234</v>
+        <v>21330051920239</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="D42" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920234</v>
+        <v>21330051920239</v>
       </c>
       <c r="B43" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C43" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="D43" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E43" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920235</v>
+        <v>21330051920240</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F44" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920235</v>
+        <v>21330051920240</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C45" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="D45" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E45" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>21330051920235</v>
+        <v>21330051920240</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="D46" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E46" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>21330051920236</v>
+        <v>21330051920241</v>
       </c>
       <c r="B47" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C47" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="D47" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
@@ -5020,16 +5023,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>21330051920236</v>
+        <v>21330051920241</v>
       </c>
       <c r="B48" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="D48" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -5040,216 +5043,216 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>21330051920236</v>
+        <v>21330051920242</v>
       </c>
       <c r="B49" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C49" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D49" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>21330051920359</v>
+        <v>21330051920242</v>
       </c>
       <c r="B50" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C50" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="D50" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>21330051920359</v>
+        <v>21330051920243</v>
       </c>
       <c r="B51" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D51" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F51" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>21330051920359</v>
+        <v>21330051920243</v>
       </c>
       <c r="B52" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D52" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E52" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>21330051920359</v>
+        <v>21330051920243</v>
       </c>
       <c r="B53" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C53" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D53" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E53" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>21330051920359</v>
+        <v>21330051920243</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C54" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D54" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E54" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F54" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>21330051920237</v>
+        <v>21330051920244</v>
       </c>
       <c r="B55" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C55" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="D55" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E55" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>21330051920237</v>
+        <v>21330051920244</v>
       </c>
       <c r="B56" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C56" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="D56" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E56" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F56" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>21330051920237</v>
+        <v>21330051920246</v>
       </c>
       <c r="B57" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C57" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="D57" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E57" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>21330051920237</v>
+        <v>21330051920246</v>
       </c>
       <c r="B58" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C58" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="D58" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E58" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>21330051920239</v>
+        <v>21330051920247</v>
       </c>
       <c r="B59" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C59" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="D59" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
@@ -5260,16 +5263,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>21330051920239</v>
+        <v>21330051920247</v>
       </c>
       <c r="B60" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C60" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="D60" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -5280,56 +5283,56 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>21330051920239</v>
+        <v>21330051920248</v>
       </c>
       <c r="B61" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C61" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="D61" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="E61" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F61" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>21330051920240</v>
+        <v>21330051920248</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C62" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D62" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="E62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>21330051920240</v>
+        <v>21330051920249</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C63" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D63" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
@@ -5340,16 +5343,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>21330051920240</v>
+        <v>21330051920249</v>
       </c>
       <c r="B64" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D64" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -5360,96 +5363,96 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>21330051920240</v>
+        <v>21330051920250</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C65" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D65" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E65" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>21330051920241</v>
+        <v>21330051920250</v>
       </c>
       <c r="B66" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C66" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="D66" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E66" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>21330051920241</v>
+        <v>21330051920229</v>
       </c>
       <c r="B67" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C67" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D67" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="E67" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F67" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>21330051920241</v>
+        <v>21330051920229</v>
       </c>
       <c r="B68" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C68" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D68" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="E68" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>21330051920242</v>
+        <v>21330051920228</v>
       </c>
       <c r="B69" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C69" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D69" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
@@ -5460,16 +5463,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>21330051920242</v>
+        <v>21330051920228</v>
       </c>
       <c r="B70" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D70" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -5480,56 +5483,56 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71">
-        <v>21330051920242</v>
+        <v>21330051920227</v>
       </c>
       <c r="B71" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C71" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D71" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E71" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F71" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>21330051920243</v>
+        <v>21330051920227</v>
       </c>
       <c r="B72" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="D72" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="E72" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F72" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>21330051920243</v>
+        <v>21330051920226</v>
       </c>
       <c r="B73" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C73" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="D73" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
@@ -5540,16 +5543,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74">
-        <v>21330051920243</v>
+        <v>21330051920226</v>
       </c>
       <c r="B74" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C74" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="D74" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -5560,116 +5563,116 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75">
-        <v>21330051920243</v>
+        <v>21330051920225</v>
       </c>
       <c r="B75" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C75" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="D75" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E75" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F75" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76">
-        <v>21330051920243</v>
+        <v>21330051920225</v>
       </c>
       <c r="B76" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C76" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="D76" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E76" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F76" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77">
-        <v>21330051920244</v>
+        <v>21330051920225</v>
       </c>
       <c r="B77" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C77" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="D77" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E77" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F77" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78">
-        <v>21330051920244</v>
+        <v>21330051920224</v>
       </c>
       <c r="B78" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C78" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D78" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E78" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F78" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79">
-        <v>21330051920244</v>
+        <v>21330051920224</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C79" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D79" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E79" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F79" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80">
-        <v>21330051920246</v>
+        <v>21330051920223</v>
       </c>
       <c r="B80" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C80" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D80" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="E80" t="s">
         <v>10</v>
@@ -5680,16 +5683,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81">
-        <v>21330051920246</v>
+        <v>21330051920223</v>
       </c>
       <c r="B81" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C81" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D81" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -5700,762 +5703,42 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82">
-        <v>21330051920246</v>
+        <v>21330051920222</v>
       </c>
       <c r="B82" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C82" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D82" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="E82" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F82" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83">
-        <v>21330051920247</v>
+        <v>21330051920222</v>
       </c>
       <c r="B83" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C83" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D83" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E83" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F83" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>21330051920247</v>
-      </c>
-      <c r="B84" t="s">
-        <v>90</v>
-      </c>
-      <c r="C84" t="s">
-        <v>115</v>
-      </c>
-      <c r="D84" t="s">
-        <v>149</v>
-      </c>
-      <c r="E84" t="s">
-        <v>8</v>
-      </c>
-      <c r="F84" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>21330051920247</v>
-      </c>
-      <c r="B85" t="s">
-        <v>90</v>
-      </c>
-      <c r="C85" t="s">
-        <v>115</v>
-      </c>
-      <c r="D85" t="s">
-        <v>149</v>
-      </c>
-      <c r="E85" t="s">
-        <v>7</v>
-      </c>
-      <c r="F85" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>21330051920248</v>
-      </c>
-      <c r="B86" t="s">
-        <v>91</v>
-      </c>
-      <c r="C86" t="s">
-        <v>116</v>
-      </c>
-      <c r="D86" t="s">
-        <v>150</v>
-      </c>
-      <c r="E86" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>21330051920248</v>
-      </c>
-      <c r="B87" t="s">
-        <v>91</v>
-      </c>
-      <c r="C87" t="s">
-        <v>116</v>
-      </c>
-      <c r="D87" t="s">
-        <v>150</v>
-      </c>
-      <c r="E87" t="s">
-        <v>8</v>
-      </c>
-      <c r="F87" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>21330051920248</v>
-      </c>
-      <c r="B88" t="s">
-        <v>91</v>
-      </c>
-      <c r="C88" t="s">
-        <v>116</v>
-      </c>
-      <c r="D88" t="s">
-        <v>150</v>
-      </c>
-      <c r="E88" t="s">
-        <v>7</v>
-      </c>
-      <c r="F88" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>21330051920249</v>
-      </c>
-      <c r="B89" t="s">
-        <v>92</v>
-      </c>
-      <c r="C89" t="s">
-        <v>117</v>
-      </c>
-      <c r="D89" t="s">
-        <v>151</v>
-      </c>
-      <c r="E89" t="s">
-        <v>10</v>
-      </c>
-      <c r="F89" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>21330051920249</v>
-      </c>
-      <c r="B90" t="s">
-        <v>92</v>
-      </c>
-      <c r="C90" t="s">
-        <v>117</v>
-      </c>
-      <c r="D90" t="s">
-        <v>151</v>
-      </c>
-      <c r="E90" t="s">
-        <v>8</v>
-      </c>
-      <c r="F90" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>21330051920249</v>
-      </c>
-      <c r="B91" t="s">
-        <v>92</v>
-      </c>
-      <c r="C91" t="s">
-        <v>117</v>
-      </c>
-      <c r="D91" t="s">
-        <v>151</v>
-      </c>
-      <c r="E91" t="s">
-        <v>7</v>
-      </c>
-      <c r="F91" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>21330051920250</v>
-      </c>
-      <c r="B92" t="s">
-        <v>93</v>
-      </c>
-      <c r="C92" t="s">
-        <v>118</v>
-      </c>
-      <c r="D92" t="s">
-        <v>152</v>
-      </c>
-      <c r="E92" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>21330051920250</v>
-      </c>
-      <c r="B93" t="s">
-        <v>93</v>
-      </c>
-      <c r="C93" t="s">
-        <v>118</v>
-      </c>
-      <c r="D93" t="s">
-        <v>152</v>
-      </c>
-      <c r="E93" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>21330051920250</v>
-      </c>
-      <c r="B94" t="s">
-        <v>93</v>
-      </c>
-      <c r="C94" t="s">
-        <v>118</v>
-      </c>
-      <c r="D94" t="s">
-        <v>152</v>
-      </c>
-      <c r="E94" t="s">
-        <v>7</v>
-      </c>
-      <c r="F94" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>21330051920229</v>
-      </c>
-      <c r="B95" t="s">
-        <v>93</v>
-      </c>
-      <c r="C95" t="s">
-        <v>88</v>
-      </c>
-      <c r="D95" t="s">
-        <v>153</v>
-      </c>
-      <c r="E95" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>21330051920229</v>
-      </c>
-      <c r="B96" t="s">
-        <v>93</v>
-      </c>
-      <c r="C96" t="s">
-        <v>88</v>
-      </c>
-      <c r="D96" t="s">
-        <v>153</v>
-      </c>
-      <c r="E96" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>21330051920229</v>
-      </c>
-      <c r="B97" t="s">
-        <v>93</v>
-      </c>
-      <c r="C97" t="s">
-        <v>88</v>
-      </c>
-      <c r="D97" t="s">
-        <v>153</v>
-      </c>
-      <c r="E97" t="s">
-        <v>7</v>
-      </c>
-      <c r="F97" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>21330051920228</v>
-      </c>
-      <c r="B98" t="s">
-        <v>94</v>
-      </c>
-      <c r="C98" t="s">
-        <v>119</v>
-      </c>
-      <c r="D98" t="s">
-        <v>154</v>
-      </c>
-      <c r="E98" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>21330051920228</v>
-      </c>
-      <c r="B99" t="s">
-        <v>94</v>
-      </c>
-      <c r="C99" t="s">
-        <v>119</v>
-      </c>
-      <c r="D99" t="s">
-        <v>154</v>
-      </c>
-      <c r="E99" t="s">
-        <v>8</v>
-      </c>
-      <c r="F99" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>21330051920228</v>
-      </c>
-      <c r="B100" t="s">
-        <v>94</v>
-      </c>
-      <c r="C100" t="s">
-        <v>119</v>
-      </c>
-      <c r="D100" t="s">
-        <v>154</v>
-      </c>
-      <c r="E100" t="s">
-        <v>7</v>
-      </c>
-      <c r="F100" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>21330051920227</v>
-      </c>
-      <c r="B101" t="s">
-        <v>95</v>
-      </c>
-      <c r="C101" t="s">
-        <v>120</v>
-      </c>
-      <c r="D101" t="s">
-        <v>155</v>
-      </c>
-      <c r="E101" t="s">
-        <v>10</v>
-      </c>
-      <c r="F101" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>21330051920227</v>
-      </c>
-      <c r="B102" t="s">
-        <v>95</v>
-      </c>
-      <c r="C102" t="s">
-        <v>120</v>
-      </c>
-      <c r="D102" t="s">
-        <v>155</v>
-      </c>
-      <c r="E102" t="s">
-        <v>8</v>
-      </c>
-      <c r="F102" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>21330051920227</v>
-      </c>
-      <c r="B103" t="s">
-        <v>95</v>
-      </c>
-      <c r="C103" t="s">
-        <v>120</v>
-      </c>
-      <c r="D103" t="s">
-        <v>155</v>
-      </c>
-      <c r="E103" t="s">
-        <v>7</v>
-      </c>
-      <c r="F103" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>21330051920226</v>
-      </c>
-      <c r="B104" t="s">
-        <v>96</v>
-      </c>
-      <c r="C104" t="s">
-        <v>121</v>
-      </c>
-      <c r="D104" t="s">
-        <v>156</v>
-      </c>
-      <c r="E104" t="s">
-        <v>10</v>
-      </c>
-      <c r="F104" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>21330051920226</v>
-      </c>
-      <c r="B105" t="s">
-        <v>96</v>
-      </c>
-      <c r="C105" t="s">
-        <v>121</v>
-      </c>
-      <c r="D105" t="s">
-        <v>156</v>
-      </c>
-      <c r="E105" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>21330051920226</v>
-      </c>
-      <c r="B106" t="s">
-        <v>96</v>
-      </c>
-      <c r="C106" t="s">
-        <v>121</v>
-      </c>
-      <c r="D106" t="s">
-        <v>156</v>
-      </c>
-      <c r="E106" t="s">
-        <v>7</v>
-      </c>
-      <c r="F106" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>21330051920225</v>
-      </c>
-      <c r="B107" t="s">
-        <v>96</v>
-      </c>
-      <c r="C107" t="s">
-        <v>122</v>
-      </c>
-      <c r="D107" t="s">
-        <v>157</v>
-      </c>
-      <c r="E107" t="s">
-        <v>10</v>
-      </c>
-      <c r="F107" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>21330051920225</v>
-      </c>
-      <c r="B108" t="s">
-        <v>96</v>
-      </c>
-      <c r="C108" t="s">
-        <v>122</v>
-      </c>
-      <c r="D108" t="s">
-        <v>157</v>
-      </c>
-      <c r="E108" t="s">
-        <v>8</v>
-      </c>
-      <c r="F108" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>21330051920225</v>
-      </c>
-      <c r="B109" t="s">
-        <v>96</v>
-      </c>
-      <c r="C109" t="s">
-        <v>122</v>
-      </c>
-      <c r="D109" t="s">
-        <v>157</v>
-      </c>
-      <c r="E109" t="s">
-        <v>7</v>
-      </c>
-      <c r="F109" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>21330051920225</v>
-      </c>
-      <c r="B110" t="s">
-        <v>96</v>
-      </c>
-      <c r="C110" t="s">
-        <v>122</v>
-      </c>
-      <c r="D110" t="s">
-        <v>157</v>
-      </c>
-      <c r="E110" t="s">
-        <v>6</v>
-      </c>
-      <c r="F110" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>21330051920224</v>
-      </c>
-      <c r="B111" t="s">
-        <v>97</v>
-      </c>
-      <c r="C111" t="s">
-        <v>103</v>
-      </c>
-      <c r="D111" t="s">
-        <v>158</v>
-      </c>
-      <c r="E111" t="s">
-        <v>10</v>
-      </c>
-      <c r="F111" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>21330051920224</v>
-      </c>
-      <c r="B112" t="s">
-        <v>97</v>
-      </c>
-      <c r="C112" t="s">
-        <v>103</v>
-      </c>
-      <c r="D112" t="s">
-        <v>158</v>
-      </c>
-      <c r="E112" t="s">
-        <v>8</v>
-      </c>
-      <c r="F112" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>21330051920224</v>
-      </c>
-      <c r="B113" t="s">
-        <v>97</v>
-      </c>
-      <c r="C113" t="s">
-        <v>103</v>
-      </c>
-      <c r="D113" t="s">
-        <v>158</v>
-      </c>
-      <c r="E113" t="s">
-        <v>7</v>
-      </c>
-      <c r="F113" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>21330051920223</v>
-      </c>
-      <c r="B114" t="s">
-        <v>98</v>
-      </c>
-      <c r="C114" t="s">
-        <v>123</v>
-      </c>
-      <c r="D114" t="s">
-        <v>159</v>
-      </c>
-      <c r="E114" t="s">
-        <v>10</v>
-      </c>
-      <c r="F114" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>21330051920223</v>
-      </c>
-      <c r="B115" t="s">
-        <v>98</v>
-      </c>
-      <c r="C115" t="s">
-        <v>123</v>
-      </c>
-      <c r="D115" t="s">
-        <v>159</v>
-      </c>
-      <c r="E115" t="s">
-        <v>8</v>
-      </c>
-      <c r="F115" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>21330051920223</v>
-      </c>
-      <c r="B116" t="s">
-        <v>98</v>
-      </c>
-      <c r="C116" t="s">
-        <v>123</v>
-      </c>
-      <c r="D116" t="s">
-        <v>159</v>
-      </c>
-      <c r="E116" t="s">
-        <v>7</v>
-      </c>
-      <c r="F116" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>21330051920222</v>
-      </c>
-      <c r="B117" t="s">
-        <v>99</v>
-      </c>
-      <c r="C117" t="s">
-        <v>108</v>
-      </c>
-      <c r="D117" t="s">
-        <v>160</v>
-      </c>
-      <c r="E117" t="s">
-        <v>10</v>
-      </c>
-      <c r="F117" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>21330051920222</v>
-      </c>
-      <c r="B118" t="s">
-        <v>99</v>
-      </c>
-      <c r="C118" t="s">
-        <v>108</v>
-      </c>
-      <c r="D118" t="s">
-        <v>160</v>
-      </c>
-      <c r="E118" t="s">
-        <v>8</v>
-      </c>
-      <c r="F118" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>21330051920222</v>
-      </c>
-      <c r="B119" t="s">
-        <v>99</v>
-      </c>
-      <c r="C119" t="s">
-        <v>108</v>
-      </c>
-      <c r="D119" t="s">
-        <v>160</v>
-      </c>
-      <c r="E119" t="s">
-        <v>7</v>
-      </c>
-      <c r="F119" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -6503,38 +5786,38 @@
         <v>140</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920243</v>
+        <v>21330051920237</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920237</v>
+        <v>21330051920243</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -6554,7 +5837,7 @@
         <v>143</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6571,7 +5854,7 @@
         <v>157</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6588,7 +5871,7 @@
         <v>124</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6605,7 +5888,7 @@
         <v>125</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6622,7 +5905,7 @@
         <v>126</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6639,7 +5922,7 @@
         <v>127</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6656,7 +5939,7 @@
         <v>128</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6673,7 +5956,7 @@
         <v>129</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6690,7 +5973,7 @@
         <v>130</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6707,7 +5990,7 @@
         <v>131</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6724,7 +6007,7 @@
         <v>132</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6741,7 +6024,7 @@
         <v>133</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6758,7 +6041,7 @@
         <v>134</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6775,7 +6058,7 @@
         <v>135</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6792,7 +6075,7 @@
         <v>136</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6809,7 +6092,7 @@
         <v>137</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6826,7 +6109,7 @@
         <v>138</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6843,7 +6126,7 @@
         <v>139</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6860,7 +6143,7 @@
         <v>142</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6877,7 +6160,7 @@
         <v>144</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -6894,7 +6177,7 @@
         <v>145</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6911,7 +6194,7 @@
         <v>147</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6928,7 +6211,7 @@
         <v>148</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6945,7 +6228,7 @@
         <v>149</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6962,7 +6245,7 @@
         <v>150</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -6979,7 +6262,7 @@
         <v>151</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -6996,7 +6279,7 @@
         <v>152</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -7013,7 +6296,7 @@
         <v>153</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -7030,7 +6313,7 @@
         <v>154</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -7047,7 +6330,7 @@
         <v>155</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -7064,7 +6347,7 @@
         <v>156</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -7081,7 +6364,7 @@
         <v>158</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -7098,7 +6381,7 @@
         <v>159</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -7115,7 +6398,7 @@
         <v>160</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -7125,7 +6408,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7155,6 +6438,1478 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920215</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920215</v>
+      </c>
+      <c r="B3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920216</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920216</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920217</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920217</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920218</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920218</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920219</v>
+      </c>
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920219</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920220</v>
+      </c>
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920220</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920221</v>
+      </c>
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920221</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920230</v>
+      </c>
+      <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920230</v>
+      </c>
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920231</v>
+      </c>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920231</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920232</v>
+      </c>
+      <c r="B20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920232</v>
+      </c>
+      <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920233</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920233</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920042</v>
+      </c>
+      <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920042</v>
+      </c>
+      <c r="B25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920044</v>
+      </c>
+      <c r="B26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>21330051920044</v>
+      </c>
+      <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>21330051920234</v>
+      </c>
+      <c r="B28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>21330051920234</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" t="s">
+        <v>137</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>21330051920235</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>21330051920235</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>21330051920236</v>
+      </c>
+      <c r="B32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>21330051920236</v>
+      </c>
+      <c r="B33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" t="s">
+        <v>139</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>21330051920239</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>21330051920239</v>
+      </c>
+      <c r="B35" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" t="s">
+        <v>142</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>21330051920241</v>
+      </c>
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" t="s">
+        <v>144</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>21330051920241</v>
+      </c>
+      <c r="B37" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" t="s">
+        <v>144</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>21330051920242</v>
+      </c>
+      <c r="B38" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>59</v>
+      </c>
+      <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>21330051920242</v>
+      </c>
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" t="s">
+        <v>145</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>21330051920244</v>
+      </c>
+      <c r="B40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" t="s">
+        <v>147</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>59</v>
+      </c>
+      <c r="G40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>21330051920244</v>
+      </c>
+      <c r="B41" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" t="s">
+        <v>107</v>
+      </c>
+      <c r="D41" t="s">
+        <v>147</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G41">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>21330051920246</v>
+      </c>
+      <c r="B42" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" t="s">
+        <v>110</v>
+      </c>
+      <c r="D42" t="s">
+        <v>148</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>59</v>
+      </c>
+      <c r="G42">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>21330051920246</v>
+      </c>
+      <c r="B43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" t="s">
+        <v>110</v>
+      </c>
+      <c r="D43" t="s">
+        <v>148</v>
+      </c>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>21330051920247</v>
+      </c>
+      <c r="B44" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44" t="s">
+        <v>149</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>59</v>
+      </c>
+      <c r="G44">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>21330051920247</v>
+      </c>
+      <c r="B45" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" t="s">
+        <v>115</v>
+      </c>
+      <c r="D45" t="s">
+        <v>149</v>
+      </c>
+      <c r="E45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" t="s">
+        <v>58</v>
+      </c>
+      <c r="G45">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>21330051920248</v>
+      </c>
+      <c r="B46" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" t="s">
+        <v>116</v>
+      </c>
+      <c r="D46" t="s">
+        <v>150</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>59</v>
+      </c>
+      <c r="G46">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>21330051920248</v>
+      </c>
+      <c r="B47" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" t="s">
+        <v>150</v>
+      </c>
+      <c r="E47" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" t="s">
+        <v>58</v>
+      </c>
+      <c r="G47">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>21330051920249</v>
+      </c>
+      <c r="B48" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D48" t="s">
+        <v>151</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>59</v>
+      </c>
+      <c r="G48">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>21330051920249</v>
+      </c>
+      <c r="B49" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" t="s">
+        <v>117</v>
+      </c>
+      <c r="D49" t="s">
+        <v>151</v>
+      </c>
+      <c r="E49" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" t="s">
+        <v>58</v>
+      </c>
+      <c r="G49">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>21330051920250</v>
+      </c>
+      <c r="B50" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" t="s">
+        <v>118</v>
+      </c>
+      <c r="D50" t="s">
+        <v>152</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>59</v>
+      </c>
+      <c r="G50">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>21330051920250</v>
+      </c>
+      <c r="B51" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" t="s">
+        <v>118</v>
+      </c>
+      <c r="D51" t="s">
+        <v>152</v>
+      </c>
+      <c r="E51" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" t="s">
+        <v>58</v>
+      </c>
+      <c r="G51">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>21330051920229</v>
+      </c>
+      <c r="B52" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" t="s">
+        <v>153</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G52">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>21330051920229</v>
+      </c>
+      <c r="B53" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53" t="s">
+        <v>153</v>
+      </c>
+      <c r="E53" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" t="s">
+        <v>58</v>
+      </c>
+      <c r="G53">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>21330051920228</v>
+      </c>
+      <c r="B54" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" t="s">
+        <v>119</v>
+      </c>
+      <c r="D54" t="s">
+        <v>154</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" t="s">
+        <v>59</v>
+      </c>
+      <c r="G54">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>21330051920228</v>
+      </c>
+      <c r="B55" t="s">
+        <v>94</v>
+      </c>
+      <c r="C55" t="s">
+        <v>119</v>
+      </c>
+      <c r="D55" t="s">
+        <v>154</v>
+      </c>
+      <c r="E55" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" t="s">
+        <v>58</v>
+      </c>
+      <c r="G55">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>21330051920227</v>
+      </c>
+      <c r="B56" t="s">
+        <v>95</v>
+      </c>
+      <c r="C56" t="s">
+        <v>120</v>
+      </c>
+      <c r="D56" t="s">
+        <v>155</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" t="s">
+        <v>59</v>
+      </c>
+      <c r="G56">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>21330051920227</v>
+      </c>
+      <c r="B57" t="s">
+        <v>95</v>
+      </c>
+      <c r="C57" t="s">
+        <v>120</v>
+      </c>
+      <c r="D57" t="s">
+        <v>155</v>
+      </c>
+      <c r="E57" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" t="s">
+        <v>58</v>
+      </c>
+      <c r="G57">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>21330051920226</v>
+      </c>
+      <c r="B58" t="s">
+        <v>96</v>
+      </c>
+      <c r="C58" t="s">
+        <v>121</v>
+      </c>
+      <c r="D58" t="s">
+        <v>156</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" t="s">
+        <v>59</v>
+      </c>
+      <c r="G58">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>21330051920226</v>
+      </c>
+      <c r="B59" t="s">
+        <v>96</v>
+      </c>
+      <c r="C59" t="s">
+        <v>121</v>
+      </c>
+      <c r="D59" t="s">
+        <v>156</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" t="s">
+        <v>58</v>
+      </c>
+      <c r="G59">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>21330051920224</v>
+      </c>
+      <c r="B60" t="s">
+        <v>97</v>
+      </c>
+      <c r="C60" t="s">
+        <v>103</v>
+      </c>
+      <c r="D60" t="s">
+        <v>158</v>
+      </c>
+      <c r="E60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" t="s">
+        <v>59</v>
+      </c>
+      <c r="G60">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>21330051920224</v>
+      </c>
+      <c r="B61" t="s">
+        <v>97</v>
+      </c>
+      <c r="C61" t="s">
+        <v>103</v>
+      </c>
+      <c r="D61" t="s">
+        <v>158</v>
+      </c>
+      <c r="E61" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" t="s">
+        <v>58</v>
+      </c>
+      <c r="G61">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62">
+        <v>21330051920223</v>
+      </c>
+      <c r="B62" t="s">
+        <v>98</v>
+      </c>
+      <c r="C62" t="s">
+        <v>123</v>
+      </c>
+      <c r="D62" t="s">
+        <v>159</v>
+      </c>
+      <c r="E62" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" t="s">
+        <v>59</v>
+      </c>
+      <c r="G62">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63">
+        <v>21330051920223</v>
+      </c>
+      <c r="B63" t="s">
+        <v>98</v>
+      </c>
+      <c r="C63" t="s">
+        <v>123</v>
+      </c>
+      <c r="D63" t="s">
+        <v>159</v>
+      </c>
+      <c r="E63" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" t="s">
+        <v>58</v>
+      </c>
+      <c r="G63">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64">
+        <v>21330051920222</v>
+      </c>
+      <c r="B64" t="s">
+        <v>99</v>
+      </c>
+      <c r="C64" t="s">
+        <v>108</v>
+      </c>
+      <c r="D64" t="s">
+        <v>160</v>
+      </c>
+      <c r="E64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" t="s">
+        <v>59</v>
+      </c>
+      <c r="G64">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65">
+        <v>21330051920222</v>
+      </c>
+      <c r="B65" t="s">
+        <v>99</v>
+      </c>
+      <c r="C65" t="s">
+        <v>108</v>
+      </c>
+      <c r="D65" t="s">
+        <v>160</v>
+      </c>
+      <c r="E65" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" t="s">
+        <v>58</v>
+      </c>
+      <c r="G65">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/2ARHM - Estadisticos 20212.xlsx
+++ b/grupos/2ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="161">
   <si>
     <t>Materia</t>
   </si>
@@ -194,15 +194,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Morales Vallejo Jorge Luis</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Morales Vallejo Jorge Luis</t>
-  </si>
-  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
@@ -224,6 +224,45 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>DIEGO ANTONIO</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>MICHELLE GUADALUPE</t>
+  </si>
+  <si>
+    <t>MIXTLI TONATI</t>
+  </si>
+  <si>
     <t>ALTAMIRANO</t>
   </si>
   <si>
@@ -254,36 +293,21 @@
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>LOMAN</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MADRIGAL</t>
   </si>
   <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
     <t>MONTERO</t>
   </si>
   <si>
     <t>PALMA</t>
   </si>
   <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -308,9 +332,6 @@
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>YOPIHUA</t>
   </si>
   <si>
@@ -359,9 +380,6 @@
     <t>CASTRO</t>
   </si>
   <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
     <t>RANGEL</t>
   </si>
   <si>
@@ -386,9 +404,6 @@
     <t>COYOHUA</t>
   </si>
   <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
@@ -440,27 +455,15 @@
     <t>FATIMA</t>
   </si>
   <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>DIEGO ANTONIO</t>
-  </si>
-  <si>
     <t>AMERICA PAOLA</t>
   </si>
   <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
     <t>MARIA DEL PILAR</t>
   </si>
   <si>
     <t>ROBERTO</t>
   </si>
   <si>
-    <t>MICHELLE GUADALUPE</t>
-  </si>
-  <si>
     <t>RAFAEL</t>
   </si>
   <si>
@@ -489,9 +492,6 @@
   </si>
   <si>
     <t>PAOLA</t>
-  </si>
-  <si>
-    <t>MIXTLI TONATI</t>
   </si>
   <si>
     <t>MARIELA</t>
@@ -995,13 +995,13 @@
         <v>9</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>10</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -1049,13 +1049,13 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1072,13 +1072,13 @@
         <v>9</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>10</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1126,13 +1126,13 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1149,13 +1149,13 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>10</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1203,13 +1203,13 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1226,13 +1226,13 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <v>9</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1280,13 +1280,13 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1303,13 +1303,13 @@
         <v>9</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F8">
         <v>10</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1357,13 +1357,13 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1380,13 +1380,13 @@
         <v>7</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F9">
         <v>8</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1434,13 +1434,13 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1457,13 +1457,13 @@
         <v>10</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F10">
         <v>10</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1511,13 +1511,13 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1534,13 +1534,13 @@
         <v>7</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F11">
         <v>9</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1588,13 +1588,13 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1611,13 +1611,13 @@
         <v>9</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F12">
         <v>9</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1665,13 +1665,13 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1688,13 +1688,13 @@
         <v>8</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F13">
         <v>10</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1742,13 +1742,13 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1765,13 +1765,13 @@
         <v>6</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F14">
         <v>8</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1819,13 +1819,13 @@
         <v>6</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1842,13 +1842,13 @@
         <v>8</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>8</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1896,13 +1896,13 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1919,13 +1919,13 @@
         <v>6</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F16">
         <v>8</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1973,13 +1973,13 @@
         <v>6</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1996,13 +1996,13 @@
         <v>7</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>8</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -2050,13 +2050,13 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2073,13 +2073,13 @@
         <v>8</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F18">
         <v>6</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2127,13 +2127,13 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2150,13 +2150,13 @@
         <v>8</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F19">
         <v>8</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2204,13 +2204,13 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2304,13 +2304,13 @@
         <v>8</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F21">
         <v>8</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2358,13 +2358,13 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2458,13 +2458,13 @@
         <v>6</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>-1</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2512,13 +2512,13 @@
         <v>6</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>-1</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2535,13 +2535,13 @@
         <v>9</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F24">
         <v>8</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2589,13 +2589,13 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2612,13 +2612,13 @@
         <v>6</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <v>8</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2666,13 +2666,13 @@
         <v>6</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2766,13 +2766,13 @@
         <v>9</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F27">
         <v>9</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2820,13 +2820,13 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2843,13 +2843,13 @@
         <v>9</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F28">
         <v>8</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2897,13 +2897,13 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2920,13 +2920,13 @@
         <v>9</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F29">
         <v>9</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -2974,13 +2974,13 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2997,13 +2997,13 @@
         <v>6</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F30">
         <v>7</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H30">
         <v>-1</v>
@@ -3051,13 +3051,13 @@
         <v>6</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3074,13 +3074,13 @@
         <v>8</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F31">
         <v>9</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3128,13 +3128,13 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3151,13 +3151,13 @@
         <v>10</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F32">
         <v>9</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3205,13 +3205,13 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3228,13 +3228,13 @@
         <v>7</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F33">
         <v>8</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3282,13 +3282,13 @@
         <v>7</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3305,13 +3305,13 @@
         <v>8</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F34">
         <v>7</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H34">
         <v>-1</v>
@@ -3359,13 +3359,13 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3382,13 +3382,13 @@
         <v>8</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F35">
         <v>9</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H35">
         <v>-1</v>
@@ -3436,13 +3436,13 @@
         <v>8</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>9</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F36">
         <v>10</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H36">
         <v>-1</v>
@@ -3513,13 +3513,13 @@
         <v>10</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X36">
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3613,13 +3613,13 @@
         <v>9</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F38">
         <v>10</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H38">
         <v>-1</v>
@@ -3667,13 +3667,13 @@
         <v>9</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X38">
         <v>10</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3690,13 +3690,13 @@
         <v>7</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F39">
         <v>9</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H39">
         <v>-1</v>
@@ -3744,13 +3744,13 @@
         <v>7</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X39">
         <v>9</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3767,13 +3767,13 @@
         <v>6</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F40">
         <v>8</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H40">
         <v>-1</v>
@@ -3821,13 +3821,13 @@
         <v>6</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>8</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
@@ -3892,27 +3892,30 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>8.699999999999999</v>
+      </c>
       <c r="I2">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -3921,27 +3924,30 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>8.5</v>
+      </c>
       <c r="I3">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -3962,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>4</v>
@@ -4074,7 +4080,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4103,19 +4109,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920215</v>
+        <v>21330051920359</v>
       </c>
       <c r="B2" t="s">
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>58</v>
@@ -4123,19 +4129,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920215</v>
+        <v>21330051920359</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>59</v>
@@ -4143,59 +4149,59 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920216</v>
+        <v>21330051920359</v>
       </c>
       <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
         <v>69</v>
       </c>
-      <c r="C4" t="s">
-        <v>101</v>
-      </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920216</v>
+        <v>21330051920359</v>
       </c>
       <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
         <v>69</v>
       </c>
-      <c r="C5" t="s">
-        <v>101</v>
-      </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920217</v>
+        <v>21330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>58</v>
@@ -4203,19 +4209,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920217</v>
+        <v>21330051920237</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>59</v>
@@ -4223,59 +4229,59 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920218</v>
+        <v>21330051920237</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920218</v>
+        <v>21330051920237</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920219</v>
+        <v>21330051920240</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>58</v>
@@ -4283,99 +4289,99 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920219</v>
+        <v>21330051920243</v>
       </c>
       <c r="B11" t="s">
         <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920220</v>
+        <v>21330051920243</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920220</v>
+        <v>21330051920243</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920221</v>
+        <v>21330051920243</v>
       </c>
       <c r="B14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s">
         <v>73</v>
       </c>
-      <c r="C14" t="s">
-        <v>105</v>
-      </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920221</v>
+        <v>21330051920225</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
         <v>59</v>
@@ -4383,1362 +4389,42 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920230</v>
+        <v>21330051920225</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920230</v>
+        <v>21330051920225</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920231</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920231</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" t="s">
-        <v>132</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920232</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920232</v>
-      </c>
-      <c r="B21" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" t="s">
-        <v>133</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920233</v>
-      </c>
-      <c r="B22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920233</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920042</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" t="s">
-        <v>135</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920042</v>
-      </c>
-      <c r="B25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" t="s">
-        <v>135</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920044</v>
-      </c>
-      <c r="B26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920044</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>110</v>
-      </c>
-      <c r="D27" t="s">
-        <v>136</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920234</v>
-      </c>
-      <c r="B28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" t="s">
-        <v>137</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920234</v>
-      </c>
-      <c r="B29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" t="s">
-        <v>137</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920235</v>
-      </c>
-      <c r="B30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" t="s">
-        <v>138</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920235</v>
-      </c>
-      <c r="B31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" t="s">
-        <v>74</v>
-      </c>
-      <c r="D31" t="s">
-        <v>138</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920236</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920236</v>
-      </c>
-      <c r="B33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>139</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920359</v>
-      </c>
-      <c r="B34" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" t="s">
-        <v>140</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920359</v>
-      </c>
-      <c r="B35" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" t="s">
-        <v>140</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920359</v>
-      </c>
-      <c r="B36" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" t="s">
-        <v>140</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920359</v>
-      </c>
-      <c r="B37" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" t="s">
-        <v>140</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920237</v>
-      </c>
-      <c r="B38" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" t="s">
-        <v>141</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920237</v>
-      </c>
-      <c r="B39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39" t="s">
-        <v>78</v>
-      </c>
-      <c r="D39" t="s">
-        <v>141</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920237</v>
-      </c>
-      <c r="B40" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" t="s">
-        <v>78</v>
-      </c>
-      <c r="D40" t="s">
-        <v>141</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920237</v>
-      </c>
-      <c r="B41" t="s">
-        <v>82</v>
-      </c>
-      <c r="C41" t="s">
-        <v>78</v>
-      </c>
-      <c r="D41" t="s">
-        <v>141</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920239</v>
-      </c>
-      <c r="B42" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" t="s">
-        <v>81</v>
-      </c>
-      <c r="D42" t="s">
-        <v>142</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920239</v>
-      </c>
-      <c r="B43" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" t="s">
-        <v>81</v>
-      </c>
-      <c r="D43" t="s">
-        <v>142</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920240</v>
-      </c>
-      <c r="B44" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" t="s">
-        <v>113</v>
-      </c>
-      <c r="D44" t="s">
-        <v>143</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920240</v>
-      </c>
-      <c r="B45" t="s">
-        <v>84</v>
-      </c>
-      <c r="C45" t="s">
-        <v>113</v>
-      </c>
-      <c r="D45" t="s">
-        <v>143</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920240</v>
-      </c>
-      <c r="B46" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" t="s">
-        <v>113</v>
-      </c>
-      <c r="D46" t="s">
-        <v>143</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920241</v>
-      </c>
-      <c r="B47" t="s">
-        <v>85</v>
-      </c>
-      <c r="C47" t="s">
-        <v>81</v>
-      </c>
-      <c r="D47" t="s">
-        <v>144</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920241</v>
-      </c>
-      <c r="B48" t="s">
-        <v>85</v>
-      </c>
-      <c r="C48" t="s">
-        <v>81</v>
-      </c>
-      <c r="D48" t="s">
-        <v>144</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920242</v>
-      </c>
-      <c r="B49" t="s">
-        <v>86</v>
-      </c>
-      <c r="C49" t="s">
-        <v>114</v>
-      </c>
-      <c r="D49" t="s">
-        <v>145</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920242</v>
-      </c>
-      <c r="B50" t="s">
-        <v>86</v>
-      </c>
-      <c r="C50" t="s">
-        <v>114</v>
-      </c>
-      <c r="D50" t="s">
-        <v>145</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920243</v>
-      </c>
-      <c r="B51" t="s">
-        <v>87</v>
-      </c>
-      <c r="C51" t="s">
-        <v>78</v>
-      </c>
-      <c r="D51" t="s">
-        <v>146</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920243</v>
-      </c>
-      <c r="B52" t="s">
-        <v>87</v>
-      </c>
-      <c r="C52" t="s">
-        <v>78</v>
-      </c>
-      <c r="D52" t="s">
-        <v>146</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920243</v>
-      </c>
-      <c r="B53" t="s">
-        <v>87</v>
-      </c>
-      <c r="C53" t="s">
-        <v>78</v>
-      </c>
-      <c r="D53" t="s">
-        <v>146</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920243</v>
-      </c>
-      <c r="B54" t="s">
-        <v>87</v>
-      </c>
-      <c r="C54" t="s">
-        <v>78</v>
-      </c>
-      <c r="D54" t="s">
-        <v>146</v>
-      </c>
-      <c r="E54" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920244</v>
-      </c>
-      <c r="B55" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" t="s">
-        <v>107</v>
-      </c>
-      <c r="D55" t="s">
-        <v>147</v>
-      </c>
-      <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920244</v>
-      </c>
-      <c r="B56" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" t="s">
-        <v>107</v>
-      </c>
-      <c r="D56" t="s">
-        <v>147</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920246</v>
-      </c>
-      <c r="B57" t="s">
-        <v>89</v>
-      </c>
-      <c r="C57" t="s">
-        <v>110</v>
-      </c>
-      <c r="D57" t="s">
-        <v>148</v>
-      </c>
-      <c r="E57" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920246</v>
-      </c>
-      <c r="B58" t="s">
-        <v>89</v>
-      </c>
-      <c r="C58" t="s">
-        <v>110</v>
-      </c>
-      <c r="D58" t="s">
-        <v>148</v>
-      </c>
-      <c r="E58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920247</v>
-      </c>
-      <c r="B59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C59" t="s">
-        <v>115</v>
-      </c>
-      <c r="D59" t="s">
-        <v>149</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920247</v>
-      </c>
-      <c r="B60" t="s">
-        <v>90</v>
-      </c>
-      <c r="C60" t="s">
-        <v>115</v>
-      </c>
-      <c r="D60" t="s">
-        <v>149</v>
-      </c>
-      <c r="E60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920248</v>
-      </c>
-      <c r="B61" t="s">
-        <v>91</v>
-      </c>
-      <c r="C61" t="s">
-        <v>116</v>
-      </c>
-      <c r="D61" t="s">
-        <v>150</v>
-      </c>
-      <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920248</v>
-      </c>
-      <c r="B62" t="s">
-        <v>91</v>
-      </c>
-      <c r="C62" t="s">
-        <v>116</v>
-      </c>
-      <c r="D62" t="s">
-        <v>150</v>
-      </c>
-      <c r="E62" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920249</v>
-      </c>
-      <c r="B63" t="s">
-        <v>92</v>
-      </c>
-      <c r="C63" t="s">
-        <v>117</v>
-      </c>
-      <c r="D63" t="s">
-        <v>151</v>
-      </c>
-      <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920249</v>
-      </c>
-      <c r="B64" t="s">
-        <v>92</v>
-      </c>
-      <c r="C64" t="s">
-        <v>117</v>
-      </c>
-      <c r="D64" t="s">
-        <v>151</v>
-      </c>
-      <c r="E64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920250</v>
-      </c>
-      <c r="B65" t="s">
-        <v>93</v>
-      </c>
-      <c r="C65" t="s">
-        <v>118</v>
-      </c>
-      <c r="D65" t="s">
-        <v>152</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920250</v>
-      </c>
-      <c r="B66" t="s">
-        <v>93</v>
-      </c>
-      <c r="C66" t="s">
-        <v>118</v>
-      </c>
-      <c r="D66" t="s">
-        <v>152</v>
-      </c>
-      <c r="E66" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920229</v>
-      </c>
-      <c r="B67" t="s">
-        <v>93</v>
-      </c>
-      <c r="C67" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" t="s">
-        <v>153</v>
-      </c>
-      <c r="E67" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920229</v>
-      </c>
-      <c r="B68" t="s">
-        <v>93</v>
-      </c>
-      <c r="C68" t="s">
-        <v>88</v>
-      </c>
-      <c r="D68" t="s">
-        <v>153</v>
-      </c>
-      <c r="E68" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920228</v>
-      </c>
-      <c r="B69" t="s">
-        <v>94</v>
-      </c>
-      <c r="C69" t="s">
-        <v>119</v>
-      </c>
-      <c r="D69" t="s">
-        <v>154</v>
-      </c>
-      <c r="E69" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920228</v>
-      </c>
-      <c r="B70" t="s">
-        <v>94</v>
-      </c>
-      <c r="C70" t="s">
-        <v>119</v>
-      </c>
-      <c r="D70" t="s">
-        <v>154</v>
-      </c>
-      <c r="E70" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920227</v>
-      </c>
-      <c r="B71" t="s">
-        <v>95</v>
-      </c>
-      <c r="C71" t="s">
-        <v>120</v>
-      </c>
-      <c r="D71" t="s">
-        <v>155</v>
-      </c>
-      <c r="E71" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920227</v>
-      </c>
-      <c r="B72" t="s">
-        <v>95</v>
-      </c>
-      <c r="C72" t="s">
-        <v>120</v>
-      </c>
-      <c r="D72" t="s">
-        <v>155</v>
-      </c>
-      <c r="E72" t="s">
-        <v>8</v>
-      </c>
-      <c r="F72" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920226</v>
-      </c>
-      <c r="B73" t="s">
-        <v>96</v>
-      </c>
-      <c r="C73" t="s">
-        <v>121</v>
-      </c>
-      <c r="D73" t="s">
-        <v>156</v>
-      </c>
-      <c r="E73" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920226</v>
-      </c>
-      <c r="B74" t="s">
-        <v>96</v>
-      </c>
-      <c r="C74" t="s">
-        <v>121</v>
-      </c>
-      <c r="D74" t="s">
-        <v>156</v>
-      </c>
-      <c r="E74" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920225</v>
-      </c>
-      <c r="B75" t="s">
-        <v>96</v>
-      </c>
-      <c r="C75" t="s">
-        <v>122</v>
-      </c>
-      <c r="D75" t="s">
-        <v>157</v>
-      </c>
-      <c r="E75" t="s">
-        <v>10</v>
-      </c>
-      <c r="F75" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920225</v>
-      </c>
-      <c r="B76" t="s">
-        <v>96</v>
-      </c>
-      <c r="C76" t="s">
-        <v>122</v>
-      </c>
-      <c r="D76" t="s">
-        <v>157</v>
-      </c>
-      <c r="E76" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920225</v>
-      </c>
-      <c r="B77" t="s">
-        <v>96</v>
-      </c>
-      <c r="C77" t="s">
-        <v>122</v>
-      </c>
-      <c r="D77" t="s">
-        <v>157</v>
-      </c>
-      <c r="E77" t="s">
-        <v>7</v>
-      </c>
-      <c r="F77" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920224</v>
-      </c>
-      <c r="B78" t="s">
-        <v>97</v>
-      </c>
-      <c r="C78" t="s">
-        <v>103</v>
-      </c>
-      <c r="D78" t="s">
-        <v>158</v>
-      </c>
-      <c r="E78" t="s">
-        <v>10</v>
-      </c>
-      <c r="F78" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920224</v>
-      </c>
-      <c r="B79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C79" t="s">
-        <v>103</v>
-      </c>
-      <c r="D79" t="s">
-        <v>158</v>
-      </c>
-      <c r="E79" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920223</v>
-      </c>
-      <c r="B80" t="s">
-        <v>98</v>
-      </c>
-      <c r="C80" t="s">
-        <v>123</v>
-      </c>
-      <c r="D80" t="s">
-        <v>159</v>
-      </c>
-      <c r="E80" t="s">
-        <v>10</v>
-      </c>
-      <c r="F80" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920223</v>
-      </c>
-      <c r="B81" t="s">
-        <v>98</v>
-      </c>
-      <c r="C81" t="s">
-        <v>123</v>
-      </c>
-      <c r="D81" t="s">
-        <v>159</v>
-      </c>
-      <c r="E81" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920222</v>
-      </c>
-      <c r="B82" t="s">
-        <v>99</v>
-      </c>
-      <c r="C82" t="s">
-        <v>108</v>
-      </c>
-      <c r="D82" t="s">
-        <v>160</v>
-      </c>
-      <c r="E82" t="s">
-        <v>10</v>
-      </c>
-      <c r="F82" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920222</v>
-      </c>
-      <c r="B83" t="s">
-        <v>99</v>
-      </c>
-      <c r="C83" t="s">
-        <v>108</v>
-      </c>
-      <c r="D83" t="s">
-        <v>160</v>
-      </c>
-      <c r="E83" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -5777,13 +4463,13 @@
         <v>21330051920359</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -5794,13 +4480,13 @@
         <v>21330051920237</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -5811,13 +4497,13 @@
         <v>21330051920243</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -5825,16 +4511,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920240</v>
+        <v>21330051920225</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5842,19 +4528,19 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920225</v>
+        <v>21330051920240</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5862,16 +4548,16 @@
         <v>21330051920215</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5879,16 +4565,16 @@
         <v>21330051920216</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5896,16 +4582,16 @@
         <v>21330051920217</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5913,16 +4599,16 @@
         <v>21330051920218</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5930,16 +4616,16 @@
         <v>21330051920219</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5947,16 +4633,16 @@
         <v>21330051920220</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5964,16 +4650,16 @@
         <v>21330051920221</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5981,16 +4667,16 @@
         <v>21330051920230</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5998,16 +4684,16 @@
         <v>21330051920231</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6015,16 +4701,16 @@
         <v>21330051920232</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6032,16 +4718,16 @@
         <v>21330051920233</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6049,16 +4735,16 @@
         <v>21330051920042</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6066,16 +4752,16 @@
         <v>21330051920044</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6083,16 +4769,16 @@
         <v>21330051920234</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6100,16 +4786,16 @@
         <v>21330051920235</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6117,16 +4803,16 @@
         <v>21330051920236</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6134,16 +4820,16 @@
         <v>21330051920239</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6151,16 +4837,16 @@
         <v>21330051920241</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -6168,16 +4854,16 @@
         <v>21330051920242</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6185,16 +4871,16 @@
         <v>21330051920244</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6202,16 +4888,16 @@
         <v>21330051920246</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6219,16 +4905,16 @@
         <v>21330051920247</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6236,16 +4922,16 @@
         <v>21330051920248</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -6253,16 +4939,16 @@
         <v>21330051920249</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -6270,16 +4956,16 @@
         <v>21330051920250</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -6287,16 +4973,16 @@
         <v>21330051920229</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -6304,16 +4990,16 @@
         <v>21330051920228</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -6321,16 +5007,16 @@
         <v>21330051920227</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -6338,16 +5024,16 @@
         <v>21330051920226</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D35" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -6355,16 +5041,16 @@
         <v>21330051920224</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
         <v>158</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6372,16 +5058,16 @@
         <v>21330051920223</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
         <v>159</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6389,16 +5075,16 @@
         <v>21330051920222</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D38" t="s">
         <v>160</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6408,7 +5094,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6440,1473 +5126,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920215</v>
+        <v>21330051920240</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920215</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G3">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920216</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920216</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920217</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920217</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920218</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920218</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" t="s">
-        <v>127</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920219</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" t="s">
-        <v>128</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920219</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920220</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920220</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" t="s">
-        <v>129</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920221</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" t="s">
-        <v>130</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920221</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" t="s">
-        <v>130</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920230</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" t="s">
-        <v>131</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920230</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920231</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920231</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" t="s">
-        <v>132</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920232</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920232</v>
-      </c>
-      <c r="B21" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" t="s">
-        <v>133</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920233</v>
-      </c>
-      <c r="B22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920233</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920042</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" t="s">
-        <v>135</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920042</v>
-      </c>
-      <c r="B25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" t="s">
-        <v>135</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>58</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920044</v>
-      </c>
-      <c r="B26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920044</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>110</v>
-      </c>
-      <c r="D27" t="s">
-        <v>136</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>58</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920234</v>
-      </c>
-      <c r="B28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" t="s">
-        <v>137</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920234</v>
-      </c>
-      <c r="B29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" t="s">
-        <v>137</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>58</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920235</v>
-      </c>
-      <c r="B30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" t="s">
-        <v>138</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>59</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920235</v>
-      </c>
-      <c r="B31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" t="s">
-        <v>74</v>
-      </c>
-      <c r="D31" t="s">
-        <v>138</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>58</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920236</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>59</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920236</v>
-      </c>
-      <c r="B33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>139</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>58</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920239</v>
-      </c>
-      <c r="B34" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" t="s">
-        <v>142</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>59</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920239</v>
-      </c>
-      <c r="B35" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" t="s">
-        <v>142</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>58</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920241</v>
-      </c>
-      <c r="B36" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" t="s">
-        <v>144</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920241</v>
-      </c>
-      <c r="B37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" t="s">
-        <v>144</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>58</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920242</v>
-      </c>
-      <c r="B38" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" t="s">
-        <v>114</v>
-      </c>
-      <c r="D38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920242</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39" t="s">
-        <v>145</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>58</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920244</v>
-      </c>
-      <c r="B40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" t="s">
-        <v>107</v>
-      </c>
-      <c r="D40" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>59</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920244</v>
-      </c>
-      <c r="B41" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" t="s">
-        <v>107</v>
-      </c>
-      <c r="D41" t="s">
-        <v>147</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>21330051920246</v>
-      </c>
-      <c r="B42" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" t="s">
-        <v>110</v>
-      </c>
-      <c r="D42" t="s">
-        <v>148</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>59</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>21330051920246</v>
-      </c>
-      <c r="B43" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" t="s">
-        <v>110</v>
-      </c>
-      <c r="D43" t="s">
-        <v>148</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G43">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>21330051920247</v>
-      </c>
-      <c r="B44" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" t="s">
-        <v>115</v>
-      </c>
-      <c r="D44" t="s">
-        <v>149</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>59</v>
-      </c>
-      <c r="G44">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>21330051920247</v>
-      </c>
-      <c r="B45" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" t="s">
-        <v>115</v>
-      </c>
-      <c r="D45" t="s">
-        <v>149</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" t="s">
-        <v>58</v>
-      </c>
-      <c r="G45">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>21330051920248</v>
-      </c>
-      <c r="B46" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" t="s">
-        <v>116</v>
-      </c>
-      <c r="D46" t="s">
-        <v>150</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>59</v>
-      </c>
-      <c r="G46">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>21330051920248</v>
-      </c>
-      <c r="B47" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" t="s">
-        <v>116</v>
-      </c>
-      <c r="D47" t="s">
-        <v>150</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s">
-        <v>58</v>
-      </c>
-      <c r="G47">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>21330051920249</v>
-      </c>
-      <c r="B48" t="s">
-        <v>92</v>
-      </c>
-      <c r="C48" t="s">
-        <v>117</v>
-      </c>
-      <c r="D48" t="s">
-        <v>151</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>59</v>
-      </c>
-      <c r="G48">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>21330051920249</v>
-      </c>
-      <c r="B49" t="s">
-        <v>92</v>
-      </c>
-      <c r="C49" t="s">
-        <v>117</v>
-      </c>
-      <c r="D49" t="s">
-        <v>151</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>58</v>
-      </c>
-      <c r="G49">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>21330051920250</v>
-      </c>
-      <c r="B50" t="s">
-        <v>93</v>
-      </c>
-      <c r="C50" t="s">
-        <v>118</v>
-      </c>
-      <c r="D50" t="s">
-        <v>152</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>59</v>
-      </c>
-      <c r="G50">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>21330051920250</v>
-      </c>
-      <c r="B51" t="s">
-        <v>93</v>
-      </c>
-      <c r="C51" t="s">
-        <v>118</v>
-      </c>
-      <c r="D51" t="s">
-        <v>152</v>
-      </c>
-      <c r="E51" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" t="s">
-        <v>58</v>
-      </c>
-      <c r="G51">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>21330051920229</v>
-      </c>
-      <c r="B52" t="s">
-        <v>93</v>
-      </c>
-      <c r="C52" t="s">
-        <v>88</v>
-      </c>
-      <c r="D52" t="s">
-        <v>153</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>59</v>
-      </c>
-      <c r="G52">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>21330051920229</v>
-      </c>
-      <c r="B53" t="s">
-        <v>93</v>
-      </c>
-      <c r="C53" t="s">
-        <v>88</v>
-      </c>
-      <c r="D53" t="s">
-        <v>153</v>
-      </c>
-      <c r="E53" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" t="s">
-        <v>58</v>
-      </c>
-      <c r="G53">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54">
-        <v>21330051920228</v>
-      </c>
-      <c r="B54" t="s">
-        <v>94</v>
-      </c>
-      <c r="C54" t="s">
-        <v>119</v>
-      </c>
-      <c r="D54" t="s">
-        <v>154</v>
-      </c>
-      <c r="E54" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>59</v>
-      </c>
-      <c r="G54">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55">
-        <v>21330051920228</v>
-      </c>
-      <c r="B55" t="s">
-        <v>94</v>
-      </c>
-      <c r="C55" t="s">
-        <v>119</v>
-      </c>
-      <c r="D55" t="s">
-        <v>154</v>
-      </c>
-      <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" t="s">
-        <v>58</v>
-      </c>
-      <c r="G55">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56">
-        <v>21330051920227</v>
-      </c>
-      <c r="B56" t="s">
-        <v>95</v>
-      </c>
-      <c r="C56" t="s">
-        <v>120</v>
-      </c>
-      <c r="D56" t="s">
-        <v>155</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>59</v>
-      </c>
-      <c r="G56">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57">
-        <v>21330051920227</v>
-      </c>
-      <c r="B57" t="s">
-        <v>95</v>
-      </c>
-      <c r="C57" t="s">
-        <v>120</v>
-      </c>
-      <c r="D57" t="s">
-        <v>155</v>
-      </c>
-      <c r="E57" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" t="s">
-        <v>58</v>
-      </c>
-      <c r="G57">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58">
-        <v>21330051920226</v>
-      </c>
-      <c r="B58" t="s">
-        <v>96</v>
-      </c>
-      <c r="C58" t="s">
-        <v>121</v>
-      </c>
-      <c r="D58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" t="s">
-        <v>59</v>
-      </c>
-      <c r="G58">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59">
-        <v>21330051920226</v>
-      </c>
-      <c r="B59" t="s">
-        <v>96</v>
-      </c>
-      <c r="C59" t="s">
-        <v>121</v>
-      </c>
-      <c r="D59" t="s">
-        <v>156</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" t="s">
-        <v>58</v>
-      </c>
-      <c r="G59">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60">
-        <v>21330051920224</v>
-      </c>
-      <c r="B60" t="s">
-        <v>97</v>
-      </c>
-      <c r="C60" t="s">
-        <v>103</v>
-      </c>
-      <c r="D60" t="s">
-        <v>158</v>
-      </c>
-      <c r="E60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" t="s">
-        <v>59</v>
-      </c>
-      <c r="G60">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61">
-        <v>21330051920224</v>
-      </c>
-      <c r="B61" t="s">
-        <v>97</v>
-      </c>
-      <c r="C61" t="s">
-        <v>103</v>
-      </c>
-      <c r="D61" t="s">
-        <v>158</v>
-      </c>
-      <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" t="s">
-        <v>58</v>
-      </c>
-      <c r="G61">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62">
-        <v>21330051920223</v>
-      </c>
-      <c r="B62" t="s">
-        <v>98</v>
-      </c>
-      <c r="C62" t="s">
-        <v>123</v>
-      </c>
-      <c r="D62" t="s">
-        <v>159</v>
-      </c>
-      <c r="E62" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" t="s">
-        <v>59</v>
-      </c>
-      <c r="G62">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63">
-        <v>21330051920223</v>
-      </c>
-      <c r="B63" t="s">
-        <v>98</v>
-      </c>
-      <c r="C63" t="s">
-        <v>123</v>
-      </c>
-      <c r="D63" t="s">
-        <v>159</v>
-      </c>
-      <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" t="s">
-        <v>58</v>
-      </c>
-      <c r="G63">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64">
-        <v>21330051920222</v>
-      </c>
-      <c r="B64" t="s">
-        <v>99</v>
-      </c>
-      <c r="C64" t="s">
-        <v>108</v>
-      </c>
-      <c r="D64" t="s">
-        <v>160</v>
-      </c>
-      <c r="E64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" t="s">
-        <v>59</v>
-      </c>
-      <c r="G64">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65">
-        <v>21330051920222</v>
-      </c>
-      <c r="B65" t="s">
-        <v>99</v>
-      </c>
-      <c r="C65" t="s">
-        <v>108</v>
-      </c>
-      <c r="D65" t="s">
-        <v>160</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>58</v>
-      </c>
-      <c r="G65">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ARHM - Estadisticos 20212.xlsx
+++ b/grupos/2ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="161">
   <si>
     <t>Materia</t>
   </si>
@@ -194,22 +194,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
     <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>NC</t>
@@ -1004,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1013,7 +1013,7 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -1081,7 +1081,7 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1090,7 +1090,7 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1126,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1158,7 +1158,7 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1167,7 +1167,7 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1235,7 +1235,7 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1244,7 +1244,7 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1312,7 +1312,7 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1321,7 +1321,7 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1348,7 +1348,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -1389,7 +1389,7 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1398,7 +1398,7 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1425,7 +1425,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>6</v>
@@ -1466,7 +1466,7 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1475,7 +1475,7 @@
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1502,7 +1502,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1543,7 +1543,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1552,7 +1552,7 @@
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1579,7 +1579,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -1588,7 +1588,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1620,7 +1620,7 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1629,7 +1629,7 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1665,7 +1665,7 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -1697,7 +1697,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1706,7 +1706,7 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1733,7 +1733,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>9</v>
@@ -1774,7 +1774,7 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1783,7 +1783,7 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1810,7 +1810,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -1851,7 +1851,7 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1860,7 +1860,7 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1928,7 +1928,7 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -1937,7 +1937,7 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1964,7 +1964,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -2005,7 +2005,7 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2014,7 +2014,7 @@
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2082,7 +2082,7 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2091,7 +2091,7 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2118,7 +2118,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -2127,7 +2127,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2159,7 +2159,7 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2168,7 +2168,7 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2204,7 +2204,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2227,7 +2227,7 @@
         <v>-1</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F20">
         <v>-1</v>
@@ -2236,7 +2236,7 @@
         <v>-1</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2245,7 +2245,7 @@
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2281,7 +2281,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>-1</v>
@@ -2313,7 +2313,7 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2322,7 +2322,7 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2349,7 +2349,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2381,7 +2381,7 @@
         <v>-1</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F22">
         <v>-1</v>
@@ -2390,7 +2390,7 @@
         <v>-1</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2399,7 +2399,7 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2426,7 +2426,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2435,7 +2435,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>-1</v>
@@ -2467,7 +2467,7 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2476,7 +2476,7 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2512,7 +2512,7 @@
         <v>6</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>-1</v>
@@ -2544,7 +2544,7 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2553,7 +2553,7 @@
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2580,7 +2580,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2589,7 +2589,7 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>8</v>
@@ -2621,7 +2621,7 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2630,7 +2630,7 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2657,7 +2657,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>7</v>
@@ -2666,7 +2666,7 @@
         <v>6</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -2689,7 +2689,7 @@
         <v>-1</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F26">
         <v>-1</v>
@@ -2698,7 +2698,7 @@
         <v>-1</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2707,7 +2707,7 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>-1</v>
@@ -2775,7 +2775,7 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2784,7 +2784,7 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -2811,7 +2811,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U27">
         <v>10</v>
@@ -2820,7 +2820,7 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2852,7 +2852,7 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2861,7 +2861,7 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2888,7 +2888,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2929,7 +2929,7 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -2938,7 +2938,7 @@
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -3006,7 +3006,7 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3015,7 +3015,7 @@
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -3051,7 +3051,7 @@
         <v>6</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -3083,7 +3083,7 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3092,7 +3092,7 @@
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3160,7 +3160,7 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3169,7 +3169,7 @@
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3237,7 +3237,7 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3246,7 +3246,7 @@
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>8</v>
@@ -3282,7 +3282,7 @@
         <v>7</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3314,7 +3314,7 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3323,7 +3323,7 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3350,7 +3350,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>8</v>
@@ -3391,7 +3391,7 @@
         <v>9</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3400,7 +3400,7 @@
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>-1</v>
@@ -3427,7 +3427,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>9</v>
@@ -3436,7 +3436,7 @@
         <v>8</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>9</v>
@@ -3468,7 +3468,7 @@
         <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3477,7 +3477,7 @@
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>-1</v>
@@ -3536,7 +3536,7 @@
         <v>-1</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F37">
         <v>10</v>
@@ -3545,7 +3545,7 @@
         <v>-1</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -3554,7 +3554,7 @@
         <v>-1</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L37">
         <v>-1</v>
@@ -3590,7 +3590,7 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -3622,7 +3622,7 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -3631,7 +3631,7 @@
         <v>-1</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
         <v>-1</v>
@@ -3667,7 +3667,7 @@
         <v>9</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X38">
         <v>10</v>
@@ -3699,7 +3699,7 @@
         <v>9</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
         <v>-1</v>
@@ -3708,7 +3708,7 @@
         <v>-1</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L39">
         <v>-1</v>
@@ -3735,7 +3735,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U39">
         <v>7</v>
@@ -3776,7 +3776,7 @@
         <v>8</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -3785,7 +3785,7 @@
         <v>-1</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
         <v>-1</v>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
@@ -3892,30 +3892,30 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>86.48999999999999</v>
+      </c>
+      <c r="G2">
+        <v>13.51</v>
+      </c>
+      <c r="H2">
+        <v>8.5</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>89.19</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>10.81</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -3936,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I3">
         <v>4</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>4</v>
@@ -4011,7 +4011,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
@@ -4032,7 +4032,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4043,7 +4043,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
@@ -4052,19 +4052,19 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>91.89</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>8.109999999999999</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4080,7 +4080,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4124,7 +4124,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4144,7 +4144,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4161,30 +4161,30 @@
         <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920359</v>
+        <v>21330051920237</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4201,10 +4201,10 @@
         <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4221,70 +4221,70 @@
         <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920237</v>
+        <v>21330051920240</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920237</v>
+        <v>21330051920243</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920240</v>
+        <v>21330051920243</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4301,129 +4301,49 @@
         <v>79</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920243</v>
+        <v>21330051920225</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920243</v>
+        <v>21330051920225</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920243</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920225</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920225</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" t="s">
-        <v>80</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920225</v>
-      </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4472,7 +4392,7 @@
         <v>76</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4489,7 +4409,7 @@
         <v>77</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4506,7 +4426,7 @@
         <v>79</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4523,7 +4443,7 @@
         <v>80</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5094,7 +5014,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5141,10 +5061,33 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920242</v>
+      </c>
+      <c r="B3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
         <v>58</v>
       </c>
-      <c r="G2">
-        <v>-1</v>
+      <c r="G3">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ARHM - Estadisticos 20212.xlsx
+++ b/grupos/2ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="161">
   <si>
     <t>Materia</t>
   </si>
@@ -194,18 +194,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
     <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
@@ -230,268 +230,268 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>AHUET</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DURAND</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOMAN</t>
+  </si>
+  <si>
+    <t>MADRIGAL</t>
+  </si>
+  <si>
     <t>MATLATECATL</t>
   </si>
   <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
     <t>PERALTA</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>ZACAMECAHUA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>GRANADOS</t>
+  </si>
+  <si>
+    <t>DE GANTE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>GALVAN</t>
+  </si>
+  <si>
+    <t>MARES</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
   </si>
   <si>
     <t>PALOMARES</t>
   </si>
   <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>ESPINOSA</t>
   </si>
   <si>
-    <t>EDUARDO</t>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>LETICIA ANETTE</t>
+  </si>
+  <si>
+    <t>ERANDI</t>
+  </si>
+  <si>
+    <t>PAZ AIDE</t>
+  </si>
+  <si>
+    <t>YARETZI VALERIA</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>LAURA EVELYN</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>DIANA ITZEL</t>
+  </si>
+  <si>
+    <t>ALONDRA VANNESSA</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>NOHEMI</t>
+  </si>
+  <si>
+    <t>ARANZA DANAE</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
   </si>
   <si>
     <t>DIEGO ANTONIO</t>
   </si>
   <si>
+    <t>AMERICA PAOLA</t>
+  </si>
+  <si>
     <t>DULCE DANIELA</t>
   </si>
   <si>
+    <t>MARIA DEL PILAR</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
     <t>MICHELLE GUADALUPE</t>
   </si>
   <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>CITLALI</t>
+  </si>
+  <si>
+    <t>ALMA PATRICIA</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
+    <t>NESTOR JOSUE</t>
+  </si>
+  <si>
+    <t>DIANA GUADALUPE</t>
+  </si>
+  <si>
+    <t>JARITZA</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
     <t>MIXTLI TONATI</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>AHUET</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DURAND</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOMAN</t>
-  </si>
-  <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>ZACAMECAHUA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>GRANADOS</t>
-  </si>
-  <si>
-    <t>DE GANTE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>GALVAN</t>
-  </si>
-  <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>LETICIA ANETTE</t>
-  </si>
-  <si>
-    <t>ERANDI</t>
-  </si>
-  <si>
-    <t>PAZ AIDE</t>
-  </si>
-  <si>
-    <t>YARETZI VALERIA</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>LAURA EVELYN</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>DIANA ITZEL</t>
-  </si>
-  <si>
-    <t>ALONDRA VANNESSA</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>NOHEMI</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>AMERICA PAOLA</t>
-  </si>
-  <si>
-    <t>MARIA DEL PILAR</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>CITLALI</t>
-  </si>
-  <si>
-    <t>ALMA PATRICIA</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>NESTOR JOSUE</t>
-  </si>
-  <si>
-    <t>DIANA GUADALUPE</t>
-  </si>
-  <si>
-    <t>JARITZA</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
   </si>
   <si>
     <t>MARIELA</t>
@@ -1007,19 +1007,19 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1046,7 +1046,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -1084,19 +1084,19 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1123,7 +1123,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -1132,7 +1132,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1161,19 +1161,19 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1209,7 +1209,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1238,19 +1238,19 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1274,7 +1274,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1315,19 +1315,19 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1351,7 +1351,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1392,19 +1392,19 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1428,7 +1428,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1440,7 +1440,7 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1469,19 +1469,19 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1517,7 +1517,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1546,19 +1546,19 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1623,19 +1623,19 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1662,7 +1662,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1700,19 +1700,19 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1748,7 +1748,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1777,19 +1777,19 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1813,10 +1813,10 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1825,7 +1825,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1854,19 +1854,19 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
         <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1893,7 +1893,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1931,19 +1931,19 @@
         <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1970,7 +1970,7 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1979,7 +1979,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2008,19 +2008,19 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2047,16 +2047,16 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>6</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2085,19 +2085,19 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2124,16 +2124,16 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>7</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2162,19 +2162,19 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
         <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2201,16 +2201,16 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>10</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2224,7 +2224,7 @@
         <v>5</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>7</v>
@@ -2233,16 +2233,16 @@
         <v>-1</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H20">
         <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>7</v>
@@ -2251,7 +2251,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2278,7 +2278,7 @@
         <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2287,7 +2287,7 @@
         <v>-1</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2316,19 +2316,19 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2352,10 +2352,10 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2364,7 +2364,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2378,25 +2378,25 @@
         <v>8</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>7</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>7</v>
@@ -2405,7 +2405,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2429,19 +2429,19 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>7</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2461,7 +2461,7 @@
         <v>6</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
         <v>6</v>
@@ -2470,10 +2470,10 @@
         <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>8</v>
@@ -2482,7 +2482,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2509,16 +2509,16 @@
         <v>8</v>
       </c>
       <c r="V23">
+        <v>5</v>
+      </c>
+      <c r="W23">
+        <v>7</v>
+      </c>
+      <c r="X23">
         <v>6</v>
       </c>
-      <c r="W23">
-        <v>7</v>
-      </c>
-      <c r="X23">
-        <v>-1</v>
-      </c>
       <c r="Y23">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2547,19 +2547,19 @@
         <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2586,7 +2586,7 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2595,7 +2595,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2624,19 +2624,19 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2663,16 +2663,16 @@
         <v>7</v>
       </c>
       <c r="V25">
+        <v>5</v>
+      </c>
+      <c r="W25">
+        <v>7</v>
+      </c>
+      <c r="X25">
+        <v>7</v>
+      </c>
+      <c r="Y25">
         <v>6</v>
-      </c>
-      <c r="W25">
-        <v>7</v>
-      </c>
-      <c r="X25">
-        <v>8</v>
-      </c>
-      <c r="Y25">
-        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2686,25 +2686,25 @@
         <v>5</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E26">
         <v>7</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>6</v>
@@ -2713,7 +2713,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2740,16 +2740,16 @@
         <v>5</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>7</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2778,19 +2778,19 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
         <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2823,7 +2823,7 @@
         <v>8</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2855,19 +2855,19 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2932,19 +2932,19 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2968,7 +2968,7 @@
         <v>9</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2980,7 +2980,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3009,19 +3009,19 @@
         <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3045,7 +3045,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>6</v>
@@ -3057,7 +3057,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3086,19 +3086,19 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
         <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3134,7 +3134,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3163,19 +3163,19 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3199,7 +3199,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3208,10 +3208,10 @@
         <v>10</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3240,19 +3240,19 @@
         <v>6</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>7</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3279,16 +3279,16 @@
         <v>8</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>7</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3317,19 +3317,19 @@
         <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
         <v>8</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3353,10 +3353,10 @@
         <v>9</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>8</v>
@@ -3394,19 +3394,19 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
         <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3471,19 +3471,19 @@
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
         <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3533,7 +3533,7 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E37">
         <v>7</v>
@@ -3542,7 +3542,7 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H37">
         <v>5</v>
@@ -3551,16 +3551,16 @@
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
         <v>6</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3587,16 +3587,16 @@
         <v>5</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W37">
         <v>7</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3625,19 +3625,19 @@
         <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
         <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3664,7 +3664,7 @@
         <v>10</v>
       </c>
       <c r="V38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3702,19 +3702,19 @@
         <v>10</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K39">
         <v>8</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3738,7 +3738,7 @@
         <v>9</v>
       </c>
       <c r="U39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V39">
         <v>7</v>
@@ -3779,19 +3779,19 @@
         <v>8</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
         <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3815,7 +3815,7 @@
         <v>9</v>
       </c>
       <c r="U40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V40">
         <v>6</v>
@@ -3827,7 +3827,7 @@
         <v>8</v>
       </c>
       <c r="Y40">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
@@ -3892,19 +3892,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>86.48999999999999</v>
+        <v>83.78</v>
       </c>
       <c r="G2">
-        <v>13.51</v>
+        <v>16.22</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -3924,30 +3924,30 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>89.19</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>13.51</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -3956,30 +3956,30 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>89.19</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>13.51</v>
       </c>
       <c r="H4">
         <v>8.5</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -3991,22 +3991,22 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>89.19</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>10.81</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4032,7 +4032,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4080,7 +4080,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4118,232 +4118,12 @@
         <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920359</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920359</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920237</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920237</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920237</v>
-      </c>
-      <c r="B7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920240</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920243</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920243</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920243</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920225</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920225</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4389,89 +4169,89 @@
         <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920237</v>
+        <v>21330051920215</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920243</v>
+        <v>21330051920216</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920225</v>
+        <v>21330051920217</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920240</v>
+        <v>21330051920218</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920215</v>
+        <v>21330051920219</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
         <v>129</v>
@@ -4482,13 +4262,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920216</v>
+        <v>21330051920220</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
         <v>130</v>
@@ -4499,13 +4279,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920217</v>
+        <v>21330051920221</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
         <v>131</v>
@@ -4516,13 +4296,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920218</v>
+        <v>21330051920230</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
         <v>132</v>
@@ -4533,13 +4313,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920219</v>
+        <v>21330051920231</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
         <v>133</v>
@@ -4550,13 +4330,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920220</v>
+        <v>21330051920232</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
         <v>134</v>
@@ -4567,13 +4347,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920221</v>
+        <v>21330051920233</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
         <v>135</v>
@@ -4584,13 +4364,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920230</v>
+        <v>21330051920042</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
         <v>136</v>
@@ -4601,13 +4381,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920231</v>
+        <v>21330051920044</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
         <v>137</v>
@@ -4618,13 +4398,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920232</v>
+        <v>21330051920234</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
         <v>138</v>
@@ -4635,13 +4415,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920233</v>
+        <v>21330051920235</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
         <v>139</v>
@@ -4652,13 +4432,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920042</v>
+        <v>21330051920236</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
         <v>140</v>
@@ -4669,13 +4449,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920044</v>
+        <v>21330051920237</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
         <v>141</v>
@@ -4686,13 +4466,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920234</v>
+        <v>21330051920239</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
         <v>142</v>
@@ -4703,13 +4483,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920235</v>
+        <v>21330051920240</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
         <v>143</v>
@@ -4720,13 +4500,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920236</v>
+        <v>21330051920241</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
         <v>144</v>
@@ -4737,13 +4517,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920239</v>
+        <v>21330051920242</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
         <v>145</v>
@@ -4754,13 +4534,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920241</v>
+        <v>21330051920243</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
         <v>146</v>
@@ -4771,13 +4551,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920242</v>
+        <v>21330051920244</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
         <v>147</v>
@@ -4788,13 +4568,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920244</v>
+        <v>21330051920246</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
         <v>148</v>
@@ -4805,13 +4585,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920246</v>
+        <v>21330051920247</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
         <v>149</v>
@@ -4822,13 +4602,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920247</v>
+        <v>21330051920248</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
         <v>150</v>
@@ -4839,13 +4619,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920248</v>
+        <v>21330051920249</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
         <v>151</v>
@@ -4856,13 +4636,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920249</v>
+        <v>21330051920250</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
         <v>152</v>
@@ -4873,13 +4653,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920250</v>
+        <v>21330051920229</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
         <v>153</v>
@@ -4890,13 +4670,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920229</v>
+        <v>21330051920228</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
         <v>154</v>
@@ -4907,13 +4687,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920228</v>
+        <v>21330051920227</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
         <v>155</v>
@@ -4924,13 +4704,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920227</v>
+        <v>21330051920226</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D34" t="s">
         <v>156</v>
@@ -4941,13 +4721,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920226</v>
+        <v>21330051920225</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
         <v>157</v>
@@ -4961,10 +4741,10 @@
         <v>21330051920224</v>
       </c>
       <c r="B36" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" t="s">
         <v>104</v>
-      </c>
-      <c r="C36" t="s">
-        <v>110</v>
       </c>
       <c r="D36" t="s">
         <v>158</v>
@@ -4978,10 +4758,10 @@
         <v>21330051920223</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D37" t="s">
         <v>159</v>
@@ -4995,10 +4775,10 @@
         <v>21330051920222</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D38" t="s">
         <v>160</v>
@@ -5014,7 +4794,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5049,44 +4829,113 @@
         <v>21330051920240</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
+        <v>21330051920240</v>
+      </c>
+      <c r="B3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
         <v>21330051920242</v>
       </c>
-      <c r="B3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920242</v>
+      </c>
+      <c r="B5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
         <v>58</v>
       </c>
-      <c r="G3">
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920235</v>
+      </c>
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ARHM - Estadisticos 20212.xlsx
+++ b/grupos/2ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="161">
   <si>
     <t>Materia</t>
   </si>
@@ -197,13 +197,13 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Morales Vallejo Jorge Luis</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
-    <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
     <t>Castro Vasquez Julieta</t>
@@ -1022,13 +1022,13 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -1037,10 +1037,10 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -1055,7 +1055,7 @@
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1099,13 +1099,13 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1114,7 +1114,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -1176,13 +1176,13 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1191,7 +1191,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1253,13 +1253,13 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1268,7 +1268,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1330,13 +1330,13 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1345,7 +1345,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1354,7 +1354,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1407,13 +1407,13 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1422,13 +1422,13 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1484,13 +1484,13 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1499,7 +1499,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1561,13 +1561,13 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1576,10 +1576,10 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -1638,13 +1638,13 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1653,7 +1653,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1715,13 +1715,13 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1730,7 +1730,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1739,7 +1739,7 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1748,7 +1748,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1792,13 +1792,13 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1807,7 +1807,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1869,13 +1869,13 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1884,13 +1884,13 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>10</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -1902,7 +1902,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1946,13 +1946,13 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -1961,7 +1961,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1979,7 +1979,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2023,13 +2023,13 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2038,7 +2038,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -2056,7 +2056,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2100,13 +2100,13 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2115,7 +2115,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -2124,7 +2124,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2133,7 +2133,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2177,13 +2177,13 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2192,7 +2192,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2210,7 +2210,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2254,13 +2254,13 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2269,13 +2269,13 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>5</v>
@@ -2331,13 +2331,13 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2346,7 +2346,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2355,7 +2355,7 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2408,13 +2408,13 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2423,13 +2423,13 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2485,13 +2485,13 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2500,7 +2500,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2509,7 +2509,7 @@
         <v>8</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2518,7 +2518,7 @@
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2562,13 +2562,13 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2577,7 +2577,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2586,7 +2586,7 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2639,13 +2639,13 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2654,13 +2654,13 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -2672,7 +2672,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2731,7 +2731,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
         <v>5</v>
@@ -2793,13 +2793,13 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2808,7 +2808,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2870,13 +2870,13 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2885,7 +2885,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2947,13 +2947,13 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -2962,13 +2962,13 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>9</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -3024,13 +3024,13 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -3039,13 +3039,13 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>7</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>6</v>
@@ -3101,13 +3101,13 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3116,7 +3116,7 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3125,7 +3125,7 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3134,7 +3134,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3178,13 +3178,13 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3193,7 +3193,7 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3255,13 +3255,13 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3270,7 +3270,7 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>8</v>
@@ -3279,7 +3279,7 @@
         <v>8</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3288,7 +3288,7 @@
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3332,13 +3332,13 @@
         <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3347,16 +3347,16 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>9</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>8</v>
@@ -3409,13 +3409,13 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3424,13 +3424,13 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>10</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3486,13 +3486,13 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -3501,7 +3501,7 @@
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3548,7 +3548,7 @@
         <v>5</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <v>5</v>
@@ -3563,13 +3563,13 @@
         <v>5</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -3578,7 +3578,7 @@
         <v>-1</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T37">
         <v>5</v>
@@ -3640,13 +3640,13 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -3655,7 +3655,7 @@
         <v>-1</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -3717,13 +3717,13 @@
         <v>9</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -3732,7 +3732,7 @@
         <v>-1</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T39">
         <v>9</v>
@@ -3794,13 +3794,13 @@
         <v>5</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -3809,13 +3809,13 @@
         <v>-1</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V40">
         <v>6</v>
@@ -3892,19 +3892,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>83.78</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="G2">
-        <v>16.22</v>
+        <v>13.51</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -3924,30 +3924,30 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>86.48999999999999</v>
+        <v>89.19</v>
       </c>
       <c r="G3">
-        <v>13.51</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H3">
         <v>8.4</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -3956,19 +3956,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>86.48999999999999</v>
+        <v>89.19</v>
       </c>
       <c r="G4">
-        <v>13.51</v>
+        <v>10.81</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3979,7 +3979,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -3988,25 +3988,25 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>89.19</v>
+        <v>94.59</v>
       </c>
       <c r="G5">
-        <v>8.109999999999999</v>
+        <v>5.41</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4020,19 +4020,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>91.89</v>
+        <v>94.59</v>
       </c>
       <c r="G6">
-        <v>8.109999999999999</v>
+        <v>5.41</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4794,7 +4794,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920240</v>
+        <v>21330051920235</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4849,93 +4849,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920240</v>
+        <v>21330051920242</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920242</v>
-      </c>
-      <c r="B4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920242</v>
-      </c>
-      <c r="B5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920235</v>
-      </c>
-      <c r="B6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ARHM - Estadisticos 20212.xlsx
+++ b/grupos/2ARHM - Estadisticos 20212.xlsx
@@ -1031,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1108,7 +1108,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1185,7 +1185,7 @@
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1262,7 +1262,7 @@
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1280,7 +1280,7 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>9</v>
@@ -1339,7 +1339,7 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1416,7 +1416,7 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1434,7 +1434,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1493,7 +1493,7 @@
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1570,7 +1570,7 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1647,7 +1647,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1665,7 +1665,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -1724,7 +1724,7 @@
         <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1801,7 +1801,7 @@
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1878,7 +1878,7 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1896,7 +1896,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2032,7 +2032,7 @@
         <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2050,7 +2050,7 @@
         <v>6</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -2109,7 +2109,7 @@
         <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2127,7 +2127,7 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>5</v>
@@ -2186,7 +2186,7 @@
         <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2263,7 +2263,7 @@
         <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2340,7 +2340,7 @@
         <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2358,7 +2358,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2417,7 +2417,7 @@
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2494,7 +2494,7 @@
         <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2571,7 +2571,7 @@
         <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2648,7 +2648,7 @@
         <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2666,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2725,7 +2725,7 @@
         <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2743,7 +2743,7 @@
         <v>5</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -2802,7 +2802,7 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2820,7 +2820,7 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2879,7 +2879,7 @@
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2956,7 +2956,7 @@
         <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3033,7 +3033,7 @@
         <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3110,7 +3110,7 @@
         <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3187,7 +3187,7 @@
         <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3264,7 +3264,7 @@
         <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3282,7 +3282,7 @@
         <v>7</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3341,7 +3341,7 @@
         <v>6</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3359,7 +3359,7 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>7</v>
@@ -3418,7 +3418,7 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -3495,7 +3495,7 @@
         <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3572,7 +3572,7 @@
         <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -3590,7 +3590,7 @@
         <v>5</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>8</v>
@@ -3649,7 +3649,7 @@
         <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -3667,7 +3667,7 @@
         <v>10</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X38">
         <v>10</v>
@@ -3726,7 +3726,7 @@
         <v>7</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -3803,7 +3803,7 @@
         <v>6</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -3821,7 +3821,7 @@
         <v>6</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>8</v>
@@ -4064,7 +4064,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/2ARHM - Estadisticos 20212.xlsx
+++ b/grupos/2ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="161">
   <si>
     <t>Materia</t>
   </si>
@@ -197,18 +197,18 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
@@ -224,223 +224,223 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>AHUET</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DURAND</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOMAN</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MADRIGAL</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>ZACAMECAHUA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>GRANADOS</t>
+  </si>
+  <si>
+    <t>DE GANTE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>GALVAN</t>
+  </si>
+  <si>
+    <t>MARES</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>LETICIA ANETTE</t>
+  </si>
+  <si>
+    <t>ERANDI</t>
+  </si>
+  <si>
+    <t>PAZ AIDE</t>
+  </si>
+  <si>
+    <t>YARETZI VALERIA</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>LAURA EVELYN</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>DIANA ITZEL</t>
+  </si>
+  <si>
+    <t>ALONDRA VANNESSA</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>NOHEMI</t>
+  </si>
+  <si>
+    <t>ARANZA DANAE</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
     <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>AHUET</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DURAND</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOMAN</t>
-  </si>
-  <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>ZACAMECAHUA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>GRANADOS</t>
-  </si>
-  <si>
-    <t>DE GANTE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>GALVAN</t>
-  </si>
-  <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>LETICIA ANETTE</t>
-  </si>
-  <si>
-    <t>ERANDI</t>
-  </si>
-  <si>
-    <t>PAZ AIDE</t>
-  </si>
-  <si>
-    <t>YARETZI VALERIA</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>LAURA EVELYN</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>DIANA ITZEL</t>
-  </si>
-  <si>
-    <t>ALONDRA VANNESSA</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>NOHEMI</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
   </si>
   <si>
     <t>DIEGO ANTONIO</t>
@@ -1034,7 +1034,7 @@
         <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>9</v>
@@ -1111,7 +1111,7 @@
         <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -1265,7 +1265,7 @@
         <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>9</v>
@@ -1342,7 +1342,7 @@
         <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>9</v>
@@ -1419,7 +1419,7 @@
         <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>9</v>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>9</v>
@@ -1573,7 +1573,7 @@
         <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>9</v>
@@ -1650,7 +1650,7 @@
         <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>9</v>
@@ -1727,7 +1727,7 @@
         <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>9</v>
@@ -1804,7 +1804,7 @@
         <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>9</v>
@@ -1881,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>7</v>
@@ -1958,7 +1958,7 @@
         <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>8</v>
@@ -2035,7 +2035,7 @@
         <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>6</v>
@@ -2112,7 +2112,7 @@
         <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>6</v>
@@ -2130,7 +2130,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2189,7 +2189,7 @@
         <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>9</v>
@@ -2230,7 +2230,7 @@
         <v>7</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -2248,7 +2248,7 @@
         <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -2266,7 +2266,7 @@
         <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>5</v>
@@ -2284,7 +2284,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2343,7 +2343,7 @@
         <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>9</v>
@@ -2402,7 +2402,7 @@
         <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -2420,7 +2420,7 @@
         <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>5</v>
@@ -2438,7 +2438,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2479,7 +2479,7 @@
         <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -2497,7 +2497,7 @@
         <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>8</v>
@@ -2574,7 +2574,7 @@
         <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
         <v>9</v>
@@ -2651,7 +2651,7 @@
         <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>9</v>
@@ -2710,7 +2710,7 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
         <v>5</v>
@@ -2728,7 +2728,7 @@
         <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>5</v>
@@ -2746,7 +2746,7 @@
         <v>6</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2805,7 +2805,7 @@
         <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>9</v>
@@ -2882,7 +2882,7 @@
         <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
         <v>9</v>
@@ -2959,7 +2959,7 @@
         <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>9</v>
@@ -3036,7 +3036,7 @@
         <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
         <v>7</v>
@@ -3113,7 +3113,7 @@
         <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>9</v>
@@ -3190,7 +3190,7 @@
         <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>10</v>
@@ -3267,7 +3267,7 @@
         <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
         <v>9</v>
@@ -3344,7 +3344,7 @@
         <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
         <v>8</v>
@@ -3421,7 +3421,7 @@
         <v>9</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
         <v>9</v>
@@ -3498,7 +3498,7 @@
         <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
         <v>10</v>
@@ -3575,7 +3575,7 @@
         <v>6</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
         <v>5</v>
@@ -3652,7 +3652,7 @@
         <v>9</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
         <v>10</v>
@@ -3729,7 +3729,7 @@
         <v>9</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
         <v>9</v>
@@ -3806,7 +3806,7 @@
         <v>6</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
         <v>8</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -3927,27 +3927,27 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>89.19</v>
       </c>
       <c r="G3">
-        <v>8.109999999999999</v>
+        <v>10.81</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -3956,19 +3956,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>89.19</v>
+        <v>94.59</v>
       </c>
       <c r="G4">
-        <v>10.81</v>
+        <v>5.41</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3979,7 +3979,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -4000,7 +4000,7 @@
         <v>5.41</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4011,7 +4011,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
@@ -4020,19 +4020,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4080,7 +4080,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4105,26 +4105,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920359</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4160,27 +4140,27 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920359</v>
+        <v>21330051920215</v>
       </c>
       <c r="B2" t="s">
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920215</v>
+        <v>21330051920216</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
         <v>101</v>
@@ -4194,13 +4174,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920216</v>
+        <v>21330051920217</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
         <v>126</v>
@@ -4211,13 +4191,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920217</v>
+        <v>21330051920218</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
         <v>127</v>
@@ -4228,10 +4208,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920218</v>
+        <v>21330051920219</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
         <v>103</v>
@@ -4245,10 +4225,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920219</v>
+        <v>21330051920220</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
         <v>104</v>
@@ -4262,10 +4242,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920220</v>
+        <v>21330051920221</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
         <v>105</v>
@@ -4279,13 +4259,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920221</v>
+        <v>21330051920230</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
         <v>131</v>
@@ -4296,13 +4276,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920230</v>
+        <v>21330051920231</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
         <v>132</v>
@@ -4313,10 +4293,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920231</v>
+        <v>21330051920232</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
         <v>107</v>
@@ -4330,10 +4310,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920232</v>
+        <v>21330051920233</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
         <v>108</v>
@@ -4347,10 +4327,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920233</v>
+        <v>21330051920042</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
         <v>109</v>
@@ -4364,10 +4344,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920042</v>
+        <v>21330051920044</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
         <v>110</v>
@@ -4381,10 +4361,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920044</v>
+        <v>21330051920234</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
         <v>111</v>
@@ -4398,13 +4378,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920234</v>
+        <v>21330051920235</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
         <v>138</v>
@@ -4415,13 +4395,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920235</v>
+        <v>21330051920236</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
         <v>139</v>
@@ -4432,13 +4412,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920236</v>
+        <v>21330051920359</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
         <v>140</v>
@@ -4452,10 +4432,10 @@
         <v>21330051920237</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
         <v>141</v>
@@ -4469,10 +4449,10 @@
         <v>21330051920239</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
         <v>142</v>
@@ -4486,10 +4466,10 @@
         <v>21330051920240</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
         <v>143</v>
@@ -4503,10 +4483,10 @@
         <v>21330051920241</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
         <v>144</v>
@@ -4520,10 +4500,10 @@
         <v>21330051920242</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
         <v>145</v>
@@ -4537,10 +4517,10 @@
         <v>21330051920243</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
         <v>146</v>
@@ -4554,10 +4534,10 @@
         <v>21330051920244</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
         <v>147</v>
@@ -4571,10 +4551,10 @@
         <v>21330051920246</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
         <v>148</v>
@@ -4588,10 +4568,10 @@
         <v>21330051920247</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
         <v>149</v>
@@ -4605,10 +4585,10 @@
         <v>21330051920248</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
         <v>150</v>
@@ -4622,10 +4602,10 @@
         <v>21330051920249</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
         <v>151</v>
@@ -4639,10 +4619,10 @@
         <v>21330051920250</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
         <v>152</v>
@@ -4656,10 +4636,10 @@
         <v>21330051920229</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
         <v>153</v>
@@ -4673,10 +4653,10 @@
         <v>21330051920228</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s">
         <v>154</v>
@@ -4690,10 +4670,10 @@
         <v>21330051920227</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
         <v>155</v>
@@ -4707,10 +4687,10 @@
         <v>21330051920226</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
         <v>156</v>
@@ -4724,10 +4704,10 @@
         <v>21330051920225</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
         <v>157</v>
@@ -4741,10 +4721,10 @@
         <v>21330051920224</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D36" t="s">
         <v>158</v>
@@ -4758,10 +4738,10 @@
         <v>21330051920223</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D37" t="s">
         <v>159</v>
@@ -4775,10 +4755,10 @@
         <v>21330051920222</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D38" t="s">
         <v>160</v>
@@ -4794,7 +4774,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4826,22 +4806,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920235</v>
+        <v>21330051920359</v>
       </c>
       <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
         <v>82</v>
       </c>
-      <c r="C2" t="s">
-        <v>77</v>
-      </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4849,24 +4829,93 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
+        <v>21330051920359</v>
+      </c>
+      <c r="B3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920237</v>
+      </c>
+      <c r="B4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920237</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
         <v>21330051920242</v>
       </c>
-      <c r="B3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" t="s">
         <v>145</v>
       </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
         <v>58</v>
       </c>
-      <c r="G3">
+      <c r="G6">
         <v>5</v>
       </c>
     </row>
